--- a/41JP Jakist program ta testuvannja/5/JP_KNT-122_Onyshchenko_19_PR5.xlsx
+++ b/41JP Jakist program ta testuvannja/5/JP_KNT-122_Onyshchenko_19_PR5.xlsx
@@ -1076,7 +1076,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="105">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1337,11 +1337,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1371,10 +1367,6 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -4589,7 +4581,7 @@
       <c r="F4" s="59"/>
       <c r="G4" s="60"/>
     </row>
-    <row r="5" customFormat="false" ht="23.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="61" t="s">
         <v>104</v>
       </c>
@@ -4624,7 +4616,7 @@
         <v>14</v>
       </c>
       <c r="E6" s="64"/>
-      <c r="F6" s="65" t="s">
+      <c r="F6" s="14" t="s">
         <v>11</v>
       </c>
       <c r="G6" s="7" t="s">
@@ -4639,7 +4631,7 @@
       <c r="C7" s="64"/>
       <c r="D7" s="64"/>
       <c r="E7" s="64"/>
-      <c r="F7" s="66" t="s">
+      <c r="F7" s="65" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="7" t="s">
@@ -4676,7 +4668,7 @@
       <c r="D9" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="67"/>
+      <c r="E9" s="66"/>
       <c r="F9" s="59"/>
       <c r="G9" s="60"/>
     </row>
@@ -4715,13 +4707,13 @@
       <c r="G11" s="60"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="68" t="s">
+      <c r="A12" s="67" t="s">
         <v>111</v>
       </c>
-      <c r="B12" s="68"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="68"/>
-      <c r="E12" s="68"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
       <c r="F12" s="59"/>
       <c r="G12" s="60"/>
     </row>
@@ -4745,13 +4737,13 @@
       <c r="G13" s="60"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="69" t="s">
+      <c r="A14" s="68" t="s">
         <v>114</v>
       </c>
-      <c r="B14" s="69"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
+      <c r="B14" s="68"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="68"/>
       <c r="F14" s="59"/>
       <c r="G14" s="60"/>
     </row>
@@ -4879,7 +4871,7 @@
       <c r="F22" s="59"/>
       <c r="G22" s="60"/>
     </row>
-    <row r="23" customFormat="false" ht="23.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
         <v>123</v>
       </c>
@@ -4961,13 +4953,13 @@
       <c r="G27" s="60"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="69" t="s">
+      <c r="A28" s="68" t="s">
         <v>114</v>
       </c>
-      <c r="B28" s="69"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
       <c r="F28" s="59"/>
       <c r="G28" s="60"/>
     </row>
@@ -4989,17 +4981,17 @@
       <c r="G29" s="60"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="70" t="s">
+      <c r="A30" s="69" t="s">
         <v>128</v>
       </c>
-      <c r="B30" s="70"/>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
+      <c r="B30" s="69"/>
+      <c r="C30" s="69"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
       <c r="F30" s="59"/>
       <c r="G30" s="60"/>
     </row>
-    <row r="31" customFormat="false" ht="34.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
         <v>129</v>
       </c>
@@ -5051,13 +5043,13 @@
       <c r="G33" s="60"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="71" t="s">
+      <c r="A34" s="70" t="s">
         <v>132</v>
       </c>
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
+      <c r="B34" s="70"/>
+      <c r="C34" s="70"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
       <c r="F34" s="59"/>
       <c r="G34" s="60"/>
     </row>
@@ -5097,7 +5089,7 @@
       <c r="F36" s="59"/>
       <c r="G36" s="60"/>
     </row>
-    <row r="37" customFormat="false" ht="23.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="63" t="s">
         <v>135</v>
       </c>
@@ -5131,7 +5123,7 @@
       <c r="F38" s="55"/>
       <c r="G38" s="56"/>
     </row>
-    <row r="39" customFormat="false" ht="23.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
         <v>137</v>
       </c>
@@ -5148,7 +5140,7 @@
       <c r="F39" s="55"/>
       <c r="G39" s="56"/>
     </row>
-    <row r="40" customFormat="false" ht="34.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="63" t="s">
         <v>138</v>
       </c>
@@ -5165,7 +5157,7 @@
       <c r="F40" s="55"/>
       <c r="G40" s="56"/>
     </row>
-    <row r="41" customFormat="false" ht="34.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="63" t="s">
         <v>139</v>
       </c>
@@ -5200,13 +5192,13 @@
       <c r="G42" s="56"/>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="72" t="s">
+      <c r="A43" s="71" t="s">
         <v>141</v>
       </c>
-      <c r="B43" s="72"/>
-      <c r="C43" s="72"/>
-      <c r="D43" s="72"/>
-      <c r="E43" s="72"/>
+      <c r="B43" s="71"/>
+      <c r="C43" s="71"/>
+      <c r="D43" s="71"/>
+      <c r="E43" s="71"/>
       <c r="F43" s="56"/>
       <c r="G43" s="56"/>
     </row>
@@ -5229,22 +5221,22 @@
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="24"/>
-      <c r="B45" s="73"/>
-      <c r="C45" s="73"/>
-      <c r="D45" s="73"/>
+      <c r="B45" s="72"/>
+      <c r="C45" s="72"/>
+      <c r="D45" s="72"/>
       <c r="E45" s="24"/>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="73"/>
-      <c r="C46" s="73"/>
-      <c r="D46" s="73"/>
+      <c r="B46" s="72"/>
+      <c r="C46" s="72"/>
+      <c r="D46" s="72"/>
       <c r="E46" s="24"/>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="74" t="s">
+      <c r="A47" s="45" t="s">
         <v>143</v>
       </c>
       <c r="B47" s="57" t="s">
@@ -5259,7 +5251,7 @@
       <c r="E47" s="45"/>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="74" t="s">
+      <c r="A48" s="45" t="s">
         <v>144</v>
       </c>
       <c r="B48" s="62" t="s">
@@ -5276,7 +5268,7 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="74" t="s">
+      <c r="A49" s="45" t="s">
         <v>145</v>
       </c>
       <c r="B49" s="57" t="s">
@@ -5291,7 +5283,7 @@
       <c r="E49" s="45"/>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="74" t="s">
+      <c r="A50" s="45" t="s">
         <v>146</v>
       </c>
       <c r="B50" s="62" t="s">
@@ -5308,7 +5300,7 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="74" t="s">
+      <c r="A51" s="45" t="s">
         <v>147</v>
       </c>
       <c r="B51" s="57" t="s">
@@ -6377,27 +6369,27 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="75"/>
-      <c r="B1" s="76" t="s">
+      <c r="A1" s="73"/>
+      <c r="B1" s="74" t="s">
         <v>148</v>
       </c>
-      <c r="C1" s="76" t="s">
+      <c r="C1" s="74" t="s">
         <v>149</v>
       </c>
-      <c r="D1" s="76" t="s">
+      <c r="D1" s="74" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="51"/>
       <c r="F1" s="52"/>
     </row>
     <row r="2" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="77"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="79" t="s">
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="81" t="s">
+      <c r="D2" s="78"/>
+      <c r="E2" s="79" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="28" t="s">
@@ -6408,15 +6400,15 @@
       <c r="A3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="82" t="s">
+      <c r="B3" s="76"/>
+      <c r="C3" s="80" t="s">
         <v>151</v>
       </c>
-      <c r="D3" s="80"/>
-      <c r="E3" s="83" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="84" t="s">
+      <c r="D3" s="78"/>
+      <c r="E3" s="81" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="82" t="s">
         <v>12</v>
       </c>
     </row>
@@ -6432,7 +6424,7 @@
       <c r="E4" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="84" t="s">
+      <c r="F4" s="82" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6443,7 +6435,7 @@
       <c r="B5" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="C5" s="85"/>
+      <c r="C5" s="83"/>
       <c r="D5" s="45"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6453,8 +6445,8 @@
       <c r="B6" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="C6" s="85"/>
-      <c r="D6" s="86"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="84"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="n">
@@ -6463,7 +6455,7 @@
       <c r="B7" s="45" t="s">
         <v>158</v>
       </c>
-      <c r="C7" s="85"/>
+      <c r="C7" s="83"/>
       <c r="D7" s="45"/>
       <c r="E7" s="24"/>
     </row>
@@ -6474,7 +6466,7 @@
       <c r="B8" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="87"/>
+      <c r="C8" s="85"/>
       <c r="D8" s="45"/>
       <c r="E8" s="24"/>
     </row>
@@ -6485,7 +6477,7 @@
       <c r="B9" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="87"/>
+      <c r="C9" s="85"/>
       <c r="D9" s="45"/>
       <c r="E9" s="24"/>
     </row>
@@ -6496,7 +6488,7 @@
       <c r="B10" s="45" t="s">
         <v>159</v>
       </c>
-      <c r="C10" s="87"/>
+      <c r="C10" s="85"/>
       <c r="D10" s="45"/>
       <c r="E10" s="24"/>
     </row>
@@ -6507,7 +6499,7 @@
       <c r="B11" s="45" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="87"/>
+      <c r="C11" s="85"/>
       <c r="D11" s="45"/>
       <c r="E11" s="24"/>
     </row>
@@ -6518,7 +6510,7 @@
       <c r="B12" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="C12" s="87"/>
+      <c r="C12" s="85"/>
       <c r="D12" s="45"/>
       <c r="E12" s="24"/>
     </row>
@@ -6534,13 +6526,13 @@
       <c r="E13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="86" t="s">
         <v>152</v>
       </c>
       <c r="B14" s="45" t="s">
         <v>163</v>
       </c>
-      <c r="C14" s="87"/>
+      <c r="C14" s="85"/>
       <c r="D14" s="45"/>
       <c r="E14" s="24"/>
     </row>
@@ -6551,7 +6543,7 @@
       <c r="B15" s="45" t="s">
         <v>164</v>
       </c>
-      <c r="C15" s="87"/>
+      <c r="C15" s="85"/>
       <c r="D15" s="45"/>
       <c r="E15" s="24"/>
     </row>
@@ -6562,7 +6554,7 @@
       <c r="B16" s="45" t="s">
         <v>165</v>
       </c>
-      <c r="C16" s="87"/>
+      <c r="C16" s="85"/>
       <c r="D16" s="45"/>
       <c r="E16" s="24"/>
     </row>
@@ -6573,7 +6565,7 @@
       <c r="B17" s="45" t="s">
         <v>167</v>
       </c>
-      <c r="C17" s="87"/>
+      <c r="C17" s="85"/>
       <c r="D17" s="45"/>
       <c r="E17" s="24"/>
     </row>
@@ -6584,51 +6576,51 @@
       <c r="B18" s="45" t="s">
         <v>169</v>
       </c>
-      <c r="C18" s="87"/>
+      <c r="C18" s="85"/>
       <c r="D18" s="45"/>
       <c r="E18" s="24"/>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="71" t="n">
+      <c r="A19" s="70" t="n">
         <v>5</v>
       </c>
       <c r="B19" s="45" t="s">
         <v>170</v>
       </c>
-      <c r="C19" s="87"/>
+      <c r="C19" s="85"/>
       <c r="D19" s="45"/>
       <c r="E19" s="24"/>
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="84" t="s">
+      <c r="A20" s="82" t="s">
         <v>152</v>
       </c>
       <c r="B20" s="45" t="s">
         <v>171</v>
       </c>
-      <c r="C20" s="87"/>
+      <c r="C20" s="85"/>
       <c r="D20" s="45"/>
       <c r="E20" s="24"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="84" t="s">
+      <c r="A21" s="82" t="s">
         <v>154</v>
       </c>
       <c r="B21" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C21" s="87"/>
+      <c r="C21" s="85"/>
       <c r="D21" s="45"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="68" t="n">
+      <c r="A22" s="67" t="n">
         <v>6</v>
       </c>
-      <c r="B22" s="89" t="s">
+      <c r="B22" s="87" t="s">
         <v>173</v>
       </c>
-      <c r="C22" s="89"/>
-      <c r="D22" s="89"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="87"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="45" t="s">
@@ -6637,7 +6629,7 @@
       <c r="B23" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="C23" s="87"/>
+      <c r="C23" s="85"/>
       <c r="D23" s="45"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6647,7 +6639,7 @@
       <c r="B24" s="45" t="s">
         <v>175</v>
       </c>
-      <c r="C24" s="87"/>
+      <c r="C24" s="85"/>
       <c r="D24" s="45"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6657,7 +6649,7 @@
       <c r="B25" s="45" t="s">
         <v>176</v>
       </c>
-      <c r="C25" s="87"/>
+      <c r="C25" s="85"/>
       <c r="D25" s="45"/>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6667,19 +6659,19 @@
       <c r="B26" s="45" t="s">
         <v>177</v>
       </c>
-      <c r="C26" s="87"/>
+      <c r="C26" s="85"/>
       <c r="D26" s="45"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="45" t="s">
         <v>168</v>
       </c>
-      <c r="B27" s="90"/>
-      <c r="C27" s="73"/>
+      <c r="B27" s="88"/>
+      <c r="C27" s="72"/>
       <c r="D27" s="24"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="91"/>
+      <c r="A28" s="89"/>
       <c r="B28" s="46" t="s">
         <v>43</v>
       </c>
@@ -6687,3035 +6679,3035 @@
       <c r="D28" s="45"/>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="91"/>
-      <c r="B29" s="92"/>
+      <c r="A29" s="89"/>
+      <c r="B29" s="90"/>
       <c r="C29" s="44"/>
       <c r="D29" s="45"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="91"/>
-      <c r="B30" s="92"/>
+      <c r="A30" s="89"/>
+      <c r="B30" s="90"/>
       <c r="C30" s="44"/>
       <c r="D30" s="45"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="91"/>
-      <c r="B31" s="92"/>
+      <c r="A31" s="89"/>
+      <c r="B31" s="90"/>
       <c r="C31" s="44"/>
       <c r="D31" s="45"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="91"/>
-      <c r="B32" s="92"/>
+      <c r="A32" s="89"/>
+      <c r="B32" s="90"/>
       <c r="C32" s="44"/>
       <c r="D32" s="45"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="91"/>
-      <c r="B33" s="92"/>
+      <c r="A33" s="89"/>
+      <c r="B33" s="90"/>
       <c r="C33" s="44"/>
       <c r="D33" s="45"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="91"/>
-      <c r="B34" s="92"/>
-      <c r="C34" s="93"/>
+      <c r="A34" s="89"/>
+      <c r="B34" s="90"/>
+      <c r="C34" s="91"/>
       <c r="D34" s="43"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="91"/>
-      <c r="B35" s="91"/>
-      <c r="C35" s="91"/>
-      <c r="D35" s="91"/>
+      <c r="A35" s="89"/>
+      <c r="B35" s="89"/>
+      <c r="C35" s="89"/>
+      <c r="D35" s="89"/>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="91"/>
-      <c r="B36" s="91"/>
-      <c r="C36" s="91"/>
-      <c r="D36" s="91"/>
+      <c r="A36" s="89"/>
+      <c r="B36" s="89"/>
+      <c r="C36" s="89"/>
+      <c r="D36" s="89"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="91"/>
-      <c r="B37" s="91"/>
-      <c r="C37" s="91"/>
-      <c r="D37" s="91"/>
+      <c r="A37" s="89"/>
+      <c r="B37" s="89"/>
+      <c r="C37" s="89"/>
+      <c r="D37" s="89"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="91"/>
-      <c r="B38" s="91"/>
-      <c r="C38" s="91"/>
-      <c r="D38" s="91"/>
+      <c r="A38" s="89"/>
+      <c r="B38" s="89"/>
+      <c r="C38" s="89"/>
+      <c r="D38" s="89"/>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="91"/>
-      <c r="B39" s="91"/>
-      <c r="C39" s="91"/>
-      <c r="D39" s="91"/>
+      <c r="A39" s="89"/>
+      <c r="B39" s="89"/>
+      <c r="C39" s="89"/>
+      <c r="D39" s="89"/>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="91"/>
-      <c r="B40" s="91"/>
-      <c r="C40" s="91"/>
-      <c r="D40" s="91"/>
+      <c r="A40" s="89"/>
+      <c r="B40" s="89"/>
+      <c r="C40" s="89"/>
+      <c r="D40" s="89"/>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="91"/>
-      <c r="B41" s="91"/>
-      <c r="C41" s="91"/>
-      <c r="D41" s="91"/>
+      <c r="A41" s="89"/>
+      <c r="B41" s="89"/>
+      <c r="C41" s="89"/>
+      <c r="D41" s="89"/>
       <c r="E41" s="24"/>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="91"/>
-      <c r="B42" s="91"/>
-      <c r="C42" s="91"/>
-      <c r="D42" s="91"/>
+      <c r="A42" s="89"/>
+      <c r="B42" s="89"/>
+      <c r="C42" s="89"/>
+      <c r="D42" s="89"/>
       <c r="E42" s="24"/>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="91"/>
-      <c r="B43" s="91"/>
-      <c r="C43" s="91"/>
-      <c r="D43" s="91"/>
+      <c r="A43" s="89"/>
+      <c r="B43" s="89"/>
+      <c r="C43" s="89"/>
+      <c r="D43" s="89"/>
       <c r="E43" s="24"/>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="91"/>
-      <c r="B44" s="91"/>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
+      <c r="A44" s="89"/>
+      <c r="B44" s="89"/>
+      <c r="C44" s="89"/>
+      <c r="D44" s="89"/>
       <c r="E44" s="24"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="91"/>
-      <c r="B45" s="91"/>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
+      <c r="A45" s="89"/>
+      <c r="B45" s="89"/>
+      <c r="C45" s="89"/>
+      <c r="D45" s="89"/>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="91"/>
-      <c r="B46" s="91"/>
-      <c r="C46" s="91"/>
-      <c r="D46" s="91"/>
+      <c r="A46" s="89"/>
+      <c r="B46" s="89"/>
+      <c r="C46" s="89"/>
+      <c r="D46" s="89"/>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="91"/>
-      <c r="B47" s="91"/>
-      <c r="C47" s="91"/>
-      <c r="D47" s="91"/>
+      <c r="A47" s="89"/>
+      <c r="B47" s="89"/>
+      <c r="C47" s="89"/>
+      <c r="D47" s="89"/>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="91"/>
-      <c r="B48" s="91"/>
-      <c r="C48" s="91"/>
-      <c r="D48" s="91"/>
+      <c r="A48" s="89"/>
+      <c r="B48" s="89"/>
+      <c r="C48" s="89"/>
+      <c r="D48" s="89"/>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="91"/>
-      <c r="B49" s="91"/>
-      <c r="C49" s="91"/>
-      <c r="D49" s="91"/>
+      <c r="A49" s="89"/>
+      <c r="B49" s="89"/>
+      <c r="C49" s="89"/>
+      <c r="D49" s="89"/>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="91"/>
-      <c r="B50" s="91"/>
-      <c r="C50" s="91"/>
-      <c r="D50" s="91"/>
+      <c r="A50" s="89"/>
+      <c r="B50" s="89"/>
+      <c r="C50" s="89"/>
+      <c r="D50" s="89"/>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="91"/>
-      <c r="B51" s="91"/>
-      <c r="C51" s="91"/>
-      <c r="D51" s="91"/>
+      <c r="A51" s="89"/>
+      <c r="B51" s="89"/>
+      <c r="C51" s="89"/>
+      <c r="D51" s="89"/>
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="91"/>
-      <c r="B52" s="91"/>
-      <c r="C52" s="91"/>
-      <c r="D52" s="91"/>
+      <c r="A52" s="89"/>
+      <c r="B52" s="89"/>
+      <c r="C52" s="89"/>
+      <c r="D52" s="89"/>
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="91"/>
-      <c r="B53" s="91"/>
-      <c r="C53" s="91"/>
-      <c r="D53" s="91"/>
+      <c r="A53" s="89"/>
+      <c r="B53" s="89"/>
+      <c r="C53" s="89"/>
+      <c r="D53" s="89"/>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="91"/>
-      <c r="B54" s="91"/>
-      <c r="C54" s="91"/>
-      <c r="D54" s="91"/>
+      <c r="A54" s="89"/>
+      <c r="B54" s="89"/>
+      <c r="C54" s="89"/>
+      <c r="D54" s="89"/>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="91"/>
-      <c r="B55" s="91"/>
-      <c r="C55" s="91"/>
-      <c r="D55" s="91"/>
+      <c r="A55" s="89"/>
+      <c r="B55" s="89"/>
+      <c r="C55" s="89"/>
+      <c r="D55" s="89"/>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="91"/>
-      <c r="B56" s="91"/>
-      <c r="C56" s="91"/>
-      <c r="D56" s="91"/>
+      <c r="A56" s="89"/>
+      <c r="B56" s="89"/>
+      <c r="C56" s="89"/>
+      <c r="D56" s="89"/>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="91"/>
-      <c r="B57" s="91"/>
-      <c r="C57" s="91"/>
-      <c r="D57" s="91"/>
+      <c r="A57" s="89"/>
+      <c r="B57" s="89"/>
+      <c r="C57" s="89"/>
+      <c r="D57" s="89"/>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="91"/>
-      <c r="B58" s="91"/>
-      <c r="C58" s="91"/>
-      <c r="D58" s="91"/>
+      <c r="A58" s="89"/>
+      <c r="B58" s="89"/>
+      <c r="C58" s="89"/>
+      <c r="D58" s="89"/>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C59" s="94"/>
+      <c r="C59" s="92"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C60" s="94"/>
+      <c r="C60" s="92"/>
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C61" s="94"/>
+      <c r="C61" s="92"/>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C62" s="94"/>
+      <c r="C62" s="92"/>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C63" s="94"/>
+      <c r="C63" s="92"/>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C64" s="94"/>
+      <c r="C64" s="92"/>
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C65" s="94"/>
+      <c r="C65" s="92"/>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C66" s="94"/>
+      <c r="C66" s="92"/>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C67" s="94"/>
+      <c r="C67" s="92"/>
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C68" s="94"/>
+      <c r="C68" s="92"/>
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C69" s="94"/>
+      <c r="C69" s="92"/>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C70" s="94"/>
+      <c r="C70" s="92"/>
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C71" s="94"/>
+      <c r="C71" s="92"/>
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C72" s="94"/>
+      <c r="C72" s="92"/>
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C73" s="94"/>
+      <c r="C73" s="92"/>
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C74" s="94"/>
+      <c r="C74" s="92"/>
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C75" s="94"/>
+      <c r="C75" s="92"/>
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C76" s="94"/>
+      <c r="C76" s="92"/>
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C77" s="94"/>
+      <c r="C77" s="92"/>
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C78" s="94"/>
+      <c r="C78" s="92"/>
     </row>
     <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C79" s="94"/>
+      <c r="C79" s="92"/>
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C80" s="94"/>
+      <c r="C80" s="92"/>
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C81" s="94"/>
+      <c r="C81" s="92"/>
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C82" s="94"/>
+      <c r="C82" s="92"/>
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C83" s="94"/>
+      <c r="C83" s="92"/>
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C84" s="94"/>
+      <c r="C84" s="92"/>
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C85" s="94"/>
+      <c r="C85" s="92"/>
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C86" s="94"/>
+      <c r="C86" s="92"/>
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C87" s="94"/>
+      <c r="C87" s="92"/>
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C88" s="94"/>
+      <c r="C88" s="92"/>
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C89" s="94"/>
+      <c r="C89" s="92"/>
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C90" s="94"/>
+      <c r="C90" s="92"/>
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C91" s="94"/>
+      <c r="C91" s="92"/>
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C92" s="94"/>
+      <c r="C92" s="92"/>
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C93" s="94"/>
+      <c r="C93" s="92"/>
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C94" s="94"/>
+      <c r="C94" s="92"/>
     </row>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C95" s="94"/>
+      <c r="C95" s="92"/>
     </row>
     <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C96" s="94"/>
+      <c r="C96" s="92"/>
     </row>
     <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C97" s="94"/>
+      <c r="C97" s="92"/>
     </row>
     <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C98" s="94"/>
+      <c r="C98" s="92"/>
     </row>
     <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C99" s="94"/>
+      <c r="C99" s="92"/>
     </row>
     <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C100" s="94"/>
+      <c r="C100" s="92"/>
     </row>
     <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C101" s="94"/>
+      <c r="C101" s="92"/>
     </row>
     <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C102" s="94"/>
+      <c r="C102" s="92"/>
     </row>
     <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C103" s="94"/>
+      <c r="C103" s="92"/>
     </row>
     <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C104" s="94"/>
+      <c r="C104" s="92"/>
     </row>
     <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C105" s="94"/>
+      <c r="C105" s="92"/>
     </row>
     <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C106" s="94"/>
+      <c r="C106" s="92"/>
     </row>
     <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C107" s="94"/>
+      <c r="C107" s="92"/>
     </row>
     <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C108" s="94"/>
+      <c r="C108" s="92"/>
     </row>
     <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C109" s="94"/>
+      <c r="C109" s="92"/>
     </row>
     <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C110" s="94"/>
+      <c r="C110" s="92"/>
     </row>
     <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C111" s="94"/>
+      <c r="C111" s="92"/>
     </row>
     <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C112" s="94"/>
+      <c r="C112" s="92"/>
     </row>
     <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C113" s="94"/>
+      <c r="C113" s="92"/>
     </row>
     <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C114" s="94"/>
+      <c r="C114" s="92"/>
     </row>
     <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C115" s="94"/>
+      <c r="C115" s="92"/>
     </row>
     <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C116" s="94"/>
+      <c r="C116" s="92"/>
     </row>
     <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C117" s="94"/>
+      <c r="C117" s="92"/>
     </row>
     <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C118" s="94"/>
+      <c r="C118" s="92"/>
     </row>
     <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C119" s="94"/>
+      <c r="C119" s="92"/>
     </row>
     <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C120" s="94"/>
+      <c r="C120" s="92"/>
     </row>
     <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C121" s="94"/>
+      <c r="C121" s="92"/>
     </row>
     <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C122" s="94"/>
+      <c r="C122" s="92"/>
     </row>
     <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C123" s="94"/>
+      <c r="C123" s="92"/>
     </row>
     <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C124" s="94"/>
+      <c r="C124" s="92"/>
     </row>
     <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C125" s="94"/>
+      <c r="C125" s="92"/>
     </row>
     <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C126" s="94"/>
+      <c r="C126" s="92"/>
     </row>
     <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C127" s="94"/>
+      <c r="C127" s="92"/>
     </row>
     <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C128" s="94"/>
+      <c r="C128" s="92"/>
     </row>
     <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C129" s="94"/>
+      <c r="C129" s="92"/>
     </row>
     <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C130" s="94"/>
+      <c r="C130" s="92"/>
     </row>
     <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C131" s="94"/>
+      <c r="C131" s="92"/>
     </row>
     <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C132" s="94"/>
+      <c r="C132" s="92"/>
     </row>
     <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C133" s="94"/>
+      <c r="C133" s="92"/>
     </row>
     <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C134" s="94"/>
+      <c r="C134" s="92"/>
     </row>
     <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C135" s="94"/>
+      <c r="C135" s="92"/>
     </row>
     <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C136" s="94"/>
+      <c r="C136" s="92"/>
     </row>
     <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C137" s="94"/>
+      <c r="C137" s="92"/>
     </row>
     <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C138" s="94"/>
+      <c r="C138" s="92"/>
     </row>
     <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C139" s="94"/>
+      <c r="C139" s="92"/>
     </row>
     <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C140" s="94"/>
+      <c r="C140" s="92"/>
     </row>
     <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C141" s="94"/>
+      <c r="C141" s="92"/>
     </row>
     <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C142" s="94"/>
+      <c r="C142" s="92"/>
     </row>
     <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C143" s="94"/>
+      <c r="C143" s="92"/>
     </row>
     <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C144" s="94"/>
+      <c r="C144" s="92"/>
     </row>
     <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C145" s="94"/>
+      <c r="C145" s="92"/>
     </row>
     <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C146" s="94"/>
+      <c r="C146" s="92"/>
     </row>
     <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C147" s="94"/>
+      <c r="C147" s="92"/>
     </row>
     <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C148" s="94"/>
+      <c r="C148" s="92"/>
     </row>
     <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C149" s="94"/>
+      <c r="C149" s="92"/>
     </row>
     <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C150" s="94"/>
+      <c r="C150" s="92"/>
     </row>
     <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C151" s="94"/>
+      <c r="C151" s="92"/>
     </row>
     <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C152" s="94"/>
+      <c r="C152" s="92"/>
     </row>
     <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C153" s="94"/>
+      <c r="C153" s="92"/>
     </row>
     <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C154" s="94"/>
+      <c r="C154" s="92"/>
     </row>
     <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C155" s="94"/>
+      <c r="C155" s="92"/>
     </row>
     <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C156" s="94"/>
+      <c r="C156" s="92"/>
     </row>
     <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C157" s="94"/>
+      <c r="C157" s="92"/>
     </row>
     <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C158" s="94"/>
+      <c r="C158" s="92"/>
     </row>
     <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C159" s="94"/>
+      <c r="C159" s="92"/>
     </row>
     <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C160" s="94"/>
+      <c r="C160" s="92"/>
     </row>
     <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C161" s="94"/>
+      <c r="C161" s="92"/>
     </row>
     <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C162" s="94"/>
+      <c r="C162" s="92"/>
     </row>
     <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C163" s="94"/>
+      <c r="C163" s="92"/>
     </row>
     <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C164" s="94"/>
+      <c r="C164" s="92"/>
     </row>
     <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C165" s="94"/>
+      <c r="C165" s="92"/>
     </row>
     <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C166" s="94"/>
+      <c r="C166" s="92"/>
     </row>
     <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C167" s="94"/>
+      <c r="C167" s="92"/>
     </row>
     <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C168" s="94"/>
+      <c r="C168" s="92"/>
     </row>
     <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C169" s="94"/>
+      <c r="C169" s="92"/>
     </row>
     <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C170" s="94"/>
+      <c r="C170" s="92"/>
     </row>
     <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C171" s="94"/>
+      <c r="C171" s="92"/>
     </row>
     <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C172" s="94"/>
+      <c r="C172" s="92"/>
     </row>
     <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C173" s="94"/>
+      <c r="C173" s="92"/>
     </row>
     <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C174" s="94"/>
+      <c r="C174" s="92"/>
     </row>
     <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C175" s="94"/>
+      <c r="C175" s="92"/>
     </row>
     <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C176" s="94"/>
+      <c r="C176" s="92"/>
     </row>
     <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C177" s="94"/>
+      <c r="C177" s="92"/>
     </row>
     <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C178" s="94"/>
+      <c r="C178" s="92"/>
     </row>
     <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C179" s="94"/>
+      <c r="C179" s="92"/>
     </row>
     <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C180" s="94"/>
+      <c r="C180" s="92"/>
     </row>
     <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C181" s="94"/>
+      <c r="C181" s="92"/>
     </row>
     <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C182" s="94"/>
+      <c r="C182" s="92"/>
     </row>
     <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C183" s="94"/>
+      <c r="C183" s="92"/>
     </row>
     <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C184" s="94"/>
+      <c r="C184" s="92"/>
     </row>
     <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C185" s="94"/>
+      <c r="C185" s="92"/>
     </row>
     <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C186" s="94"/>
+      <c r="C186" s="92"/>
     </row>
     <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C187" s="94"/>
+      <c r="C187" s="92"/>
     </row>
     <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C188" s="94"/>
+      <c r="C188" s="92"/>
     </row>
     <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C189" s="94"/>
+      <c r="C189" s="92"/>
     </row>
     <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C190" s="94"/>
+      <c r="C190" s="92"/>
     </row>
     <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C191" s="94"/>
+      <c r="C191" s="92"/>
     </row>
     <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C192" s="94"/>
+      <c r="C192" s="92"/>
     </row>
     <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C193" s="94"/>
+      <c r="C193" s="92"/>
     </row>
     <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C194" s="94"/>
+      <c r="C194" s="92"/>
     </row>
     <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C195" s="94"/>
+      <c r="C195" s="92"/>
     </row>
     <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C196" s="94"/>
+      <c r="C196" s="92"/>
     </row>
     <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C197" s="94"/>
+      <c r="C197" s="92"/>
     </row>
     <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C198" s="94"/>
+      <c r="C198" s="92"/>
     </row>
     <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C199" s="94"/>
+      <c r="C199" s="92"/>
     </row>
     <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C200" s="94"/>
+      <c r="C200" s="92"/>
     </row>
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C201" s="94"/>
+      <c r="C201" s="92"/>
     </row>
     <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C202" s="94"/>
+      <c r="C202" s="92"/>
     </row>
     <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C203" s="94"/>
+      <c r="C203" s="92"/>
     </row>
     <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C204" s="94"/>
+      <c r="C204" s="92"/>
     </row>
     <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C205" s="94"/>
+      <c r="C205" s="92"/>
     </row>
     <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C206" s="94"/>
+      <c r="C206" s="92"/>
     </row>
     <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C207" s="94"/>
+      <c r="C207" s="92"/>
     </row>
     <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C208" s="94"/>
+      <c r="C208" s="92"/>
     </row>
     <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C209" s="94"/>
+      <c r="C209" s="92"/>
     </row>
     <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C210" s="94"/>
+      <c r="C210" s="92"/>
     </row>
     <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C211" s="94"/>
+      <c r="C211" s="92"/>
     </row>
     <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C212" s="94"/>
+      <c r="C212" s="92"/>
     </row>
     <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C213" s="94"/>
+      <c r="C213" s="92"/>
     </row>
     <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C214" s="94"/>
+      <c r="C214" s="92"/>
     </row>
     <row r="215" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C215" s="94"/>
+      <c r="C215" s="92"/>
     </row>
     <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C216" s="94"/>
+      <c r="C216" s="92"/>
     </row>
     <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C217" s="94"/>
+      <c r="C217" s="92"/>
     </row>
     <row r="218" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C218" s="94"/>
+      <c r="C218" s="92"/>
     </row>
     <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C219" s="94"/>
+      <c r="C219" s="92"/>
     </row>
     <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C220" s="94"/>
+      <c r="C220" s="92"/>
     </row>
     <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C221" s="94"/>
+      <c r="C221" s="92"/>
     </row>
     <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C222" s="94"/>
+      <c r="C222" s="92"/>
     </row>
     <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C223" s="94"/>
+      <c r="C223" s="92"/>
     </row>
     <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C224" s="94"/>
+      <c r="C224" s="92"/>
     </row>
     <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C225" s="94"/>
+      <c r="C225" s="92"/>
     </row>
     <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C226" s="94"/>
+      <c r="C226" s="92"/>
     </row>
     <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C227" s="94"/>
+      <c r="C227" s="92"/>
     </row>
     <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C228" s="94"/>
+      <c r="C228" s="92"/>
     </row>
     <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C229" s="94"/>
+      <c r="C229" s="92"/>
     </row>
     <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C230" s="94"/>
+      <c r="C230" s="92"/>
     </row>
     <row r="231" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C231" s="94"/>
+      <c r="C231" s="92"/>
     </row>
     <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C232" s="94"/>
+      <c r="C232" s="92"/>
     </row>
     <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C233" s="94"/>
+      <c r="C233" s="92"/>
     </row>
     <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C234" s="94"/>
+      <c r="C234" s="92"/>
     </row>
     <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C235" s="94"/>
+      <c r="C235" s="92"/>
     </row>
     <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C236" s="94"/>
+      <c r="C236" s="92"/>
     </row>
     <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C237" s="94"/>
+      <c r="C237" s="92"/>
     </row>
     <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C238" s="94"/>
+      <c r="C238" s="92"/>
     </row>
     <row r="239" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C239" s="94"/>
+      <c r="C239" s="92"/>
     </row>
     <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C240" s="94"/>
+      <c r="C240" s="92"/>
     </row>
     <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C241" s="94"/>
+      <c r="C241" s="92"/>
     </row>
     <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C242" s="94"/>
+      <c r="C242" s="92"/>
     </row>
     <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C243" s="94"/>
+      <c r="C243" s="92"/>
     </row>
     <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C244" s="94"/>
+      <c r="C244" s="92"/>
     </row>
     <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C245" s="94"/>
+      <c r="C245" s="92"/>
     </row>
     <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C246" s="94"/>
+      <c r="C246" s="92"/>
     </row>
     <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C247" s="94"/>
+      <c r="C247" s="92"/>
     </row>
     <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C248" s="94"/>
+      <c r="C248" s="92"/>
     </row>
     <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C249" s="94"/>
+      <c r="C249" s="92"/>
     </row>
     <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C250" s="94"/>
+      <c r="C250" s="92"/>
     </row>
     <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C251" s="94"/>
+      <c r="C251" s="92"/>
     </row>
     <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C252" s="94"/>
+      <c r="C252" s="92"/>
     </row>
     <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C253" s="94"/>
+      <c r="C253" s="92"/>
     </row>
     <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C254" s="94"/>
+      <c r="C254" s="92"/>
     </row>
     <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C255" s="94"/>
+      <c r="C255" s="92"/>
     </row>
     <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C256" s="94"/>
+      <c r="C256" s="92"/>
     </row>
     <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C257" s="94"/>
+      <c r="C257" s="92"/>
     </row>
     <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C258" s="94"/>
+      <c r="C258" s="92"/>
     </row>
     <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C259" s="94"/>
+      <c r="C259" s="92"/>
     </row>
     <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C260" s="94"/>
+      <c r="C260" s="92"/>
     </row>
     <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C261" s="94"/>
+      <c r="C261" s="92"/>
     </row>
     <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C262" s="94"/>
+      <c r="C262" s="92"/>
     </row>
     <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C263" s="94"/>
+      <c r="C263" s="92"/>
     </row>
     <row r="264" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C264" s="94"/>
+      <c r="C264" s="92"/>
     </row>
     <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C265" s="94"/>
+      <c r="C265" s="92"/>
     </row>
     <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C266" s="94"/>
+      <c r="C266" s="92"/>
     </row>
     <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C267" s="94"/>
+      <c r="C267" s="92"/>
     </row>
     <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C268" s="94"/>
+      <c r="C268" s="92"/>
     </row>
     <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C269" s="94"/>
+      <c r="C269" s="92"/>
     </row>
     <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C270" s="94"/>
+      <c r="C270" s="92"/>
     </row>
     <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C271" s="94"/>
+      <c r="C271" s="92"/>
     </row>
     <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C272" s="94"/>
+      <c r="C272" s="92"/>
     </row>
     <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C273" s="94"/>
+      <c r="C273" s="92"/>
     </row>
     <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C274" s="94"/>
+      <c r="C274" s="92"/>
     </row>
     <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C275" s="94"/>
+      <c r="C275" s="92"/>
     </row>
     <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C276" s="94"/>
+      <c r="C276" s="92"/>
     </row>
     <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C277" s="94"/>
+      <c r="C277" s="92"/>
     </row>
     <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C278" s="94"/>
+      <c r="C278" s="92"/>
     </row>
     <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C279" s="94"/>
+      <c r="C279" s="92"/>
     </row>
     <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C280" s="94"/>
+      <c r="C280" s="92"/>
     </row>
     <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C281" s="94"/>
+      <c r="C281" s="92"/>
     </row>
     <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C282" s="94"/>
+      <c r="C282" s="92"/>
     </row>
     <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C283" s="94"/>
+      <c r="C283" s="92"/>
     </row>
     <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C284" s="94"/>
+      <c r="C284" s="92"/>
     </row>
     <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C285" s="94"/>
+      <c r="C285" s="92"/>
     </row>
     <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C286" s="94"/>
+      <c r="C286" s="92"/>
     </row>
     <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C287" s="94"/>
+      <c r="C287" s="92"/>
     </row>
     <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C288" s="94"/>
+      <c r="C288" s="92"/>
     </row>
     <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C289" s="94"/>
+      <c r="C289" s="92"/>
     </row>
     <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C290" s="94"/>
+      <c r="C290" s="92"/>
     </row>
     <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C291" s="94"/>
+      <c r="C291" s="92"/>
     </row>
     <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C292" s="94"/>
+      <c r="C292" s="92"/>
     </row>
     <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C293" s="94"/>
+      <c r="C293" s="92"/>
     </row>
     <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C294" s="94"/>
+      <c r="C294" s="92"/>
     </row>
     <row r="295" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C295" s="94"/>
+      <c r="C295" s="92"/>
     </row>
     <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C296" s="94"/>
+      <c r="C296" s="92"/>
     </row>
     <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C297" s="94"/>
+      <c r="C297" s="92"/>
     </row>
     <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C298" s="94"/>
+      <c r="C298" s="92"/>
     </row>
     <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C299" s="94"/>
+      <c r="C299" s="92"/>
     </row>
     <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C300" s="94"/>
+      <c r="C300" s="92"/>
     </row>
     <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C301" s="94"/>
+      <c r="C301" s="92"/>
     </row>
     <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C302" s="94"/>
+      <c r="C302" s="92"/>
     </row>
     <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C303" s="94"/>
+      <c r="C303" s="92"/>
     </row>
     <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C304" s="94"/>
+      <c r="C304" s="92"/>
     </row>
     <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C305" s="94"/>
+      <c r="C305" s="92"/>
     </row>
     <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C306" s="94"/>
+      <c r="C306" s="92"/>
     </row>
     <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C307" s="94"/>
+      <c r="C307" s="92"/>
     </row>
     <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C308" s="94"/>
+      <c r="C308" s="92"/>
     </row>
     <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C309" s="94"/>
+      <c r="C309" s="92"/>
     </row>
     <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C310" s="94"/>
+      <c r="C310" s="92"/>
     </row>
     <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C311" s="94"/>
+      <c r="C311" s="92"/>
     </row>
     <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C312" s="94"/>
+      <c r="C312" s="92"/>
     </row>
     <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C313" s="94"/>
+      <c r="C313" s="92"/>
     </row>
     <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C314" s="94"/>
+      <c r="C314" s="92"/>
     </row>
     <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C315" s="94"/>
+      <c r="C315" s="92"/>
     </row>
     <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C316" s="94"/>
+      <c r="C316" s="92"/>
     </row>
     <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C317" s="94"/>
+      <c r="C317" s="92"/>
     </row>
     <row r="318" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C318" s="94"/>
+      <c r="C318" s="92"/>
     </row>
     <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C319" s="94"/>
+      <c r="C319" s="92"/>
     </row>
     <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C320" s="94"/>
+      <c r="C320" s="92"/>
     </row>
     <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C321" s="94"/>
+      <c r="C321" s="92"/>
     </row>
     <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C322" s="94"/>
+      <c r="C322" s="92"/>
     </row>
     <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C323" s="94"/>
+      <c r="C323" s="92"/>
     </row>
     <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C324" s="94"/>
+      <c r="C324" s="92"/>
     </row>
     <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C325" s="94"/>
+      <c r="C325" s="92"/>
     </row>
     <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C326" s="94"/>
+      <c r="C326" s="92"/>
     </row>
     <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C327" s="94"/>
+      <c r="C327" s="92"/>
     </row>
     <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C328" s="94"/>
+      <c r="C328" s="92"/>
     </row>
     <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C329" s="94"/>
+      <c r="C329" s="92"/>
     </row>
     <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C330" s="94"/>
+      <c r="C330" s="92"/>
     </row>
     <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C331" s="94"/>
+      <c r="C331" s="92"/>
     </row>
     <row r="332" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C332" s="94"/>
+      <c r="C332" s="92"/>
     </row>
     <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C333" s="94"/>
+      <c r="C333" s="92"/>
     </row>
     <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C334" s="94"/>
+      <c r="C334" s="92"/>
     </row>
     <row r="335" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C335" s="94"/>
+      <c r="C335" s="92"/>
     </row>
     <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C336" s="94"/>
+      <c r="C336" s="92"/>
     </row>
     <row r="337" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C337" s="94"/>
+      <c r="C337" s="92"/>
     </row>
     <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C338" s="94"/>
+      <c r="C338" s="92"/>
     </row>
     <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C339" s="94"/>
+      <c r="C339" s="92"/>
     </row>
     <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C340" s="94"/>
+      <c r="C340" s="92"/>
     </row>
     <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C341" s="94"/>
+      <c r="C341" s="92"/>
     </row>
     <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C342" s="94"/>
+      <c r="C342" s="92"/>
     </row>
     <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C343" s="94"/>
+      <c r="C343" s="92"/>
     </row>
     <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C344" s="94"/>
+      <c r="C344" s="92"/>
     </row>
     <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C345" s="94"/>
+      <c r="C345" s="92"/>
     </row>
     <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C346" s="94"/>
+      <c r="C346" s="92"/>
     </row>
     <row r="347" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C347" s="94"/>
+      <c r="C347" s="92"/>
     </row>
     <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C348" s="94"/>
+      <c r="C348" s="92"/>
     </row>
     <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C349" s="94"/>
+      <c r="C349" s="92"/>
     </row>
     <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C350" s="94"/>
+      <c r="C350" s="92"/>
     </row>
     <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C351" s="94"/>
+      <c r="C351" s="92"/>
     </row>
     <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C352" s="94"/>
+      <c r="C352" s="92"/>
     </row>
     <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C353" s="94"/>
+      <c r="C353" s="92"/>
     </row>
     <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C354" s="94"/>
+      <c r="C354" s="92"/>
     </row>
     <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C355" s="94"/>
+      <c r="C355" s="92"/>
     </row>
     <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C356" s="94"/>
+      <c r="C356" s="92"/>
     </row>
     <row r="357" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C357" s="94"/>
+      <c r="C357" s="92"/>
     </row>
     <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C358" s="94"/>
+      <c r="C358" s="92"/>
     </row>
     <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C359" s="94"/>
+      <c r="C359" s="92"/>
     </row>
     <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C360" s="94"/>
+      <c r="C360" s="92"/>
     </row>
     <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C361" s="94"/>
+      <c r="C361" s="92"/>
     </row>
     <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C362" s="94"/>
+      <c r="C362" s="92"/>
     </row>
     <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C363" s="94"/>
+      <c r="C363" s="92"/>
     </row>
     <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C364" s="94"/>
+      <c r="C364" s="92"/>
     </row>
     <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C365" s="94"/>
+      <c r="C365" s="92"/>
     </row>
     <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C366" s="94"/>
+      <c r="C366" s="92"/>
     </row>
     <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C367" s="94"/>
+      <c r="C367" s="92"/>
     </row>
     <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C368" s="94"/>
+      <c r="C368" s="92"/>
     </row>
     <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C369" s="94"/>
+      <c r="C369" s="92"/>
     </row>
     <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C370" s="94"/>
+      <c r="C370" s="92"/>
     </row>
     <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C371" s="94"/>
+      <c r="C371" s="92"/>
     </row>
     <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C372" s="94"/>
+      <c r="C372" s="92"/>
     </row>
     <row r="373" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C373" s="94"/>
+      <c r="C373" s="92"/>
     </row>
     <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C374" s="94"/>
+      <c r="C374" s="92"/>
     </row>
     <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C375" s="94"/>
+      <c r="C375" s="92"/>
     </row>
     <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C376" s="94"/>
+      <c r="C376" s="92"/>
     </row>
     <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C377" s="94"/>
+      <c r="C377" s="92"/>
     </row>
     <row r="378" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C378" s="94"/>
+      <c r="C378" s="92"/>
     </row>
     <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C379" s="94"/>
+      <c r="C379" s="92"/>
     </row>
     <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C380" s="94"/>
+      <c r="C380" s="92"/>
     </row>
     <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C381" s="94"/>
+      <c r="C381" s="92"/>
     </row>
     <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C382" s="94"/>
+      <c r="C382" s="92"/>
     </row>
     <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C383" s="94"/>
+      <c r="C383" s="92"/>
     </row>
     <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C384" s="94"/>
+      <c r="C384" s="92"/>
     </row>
     <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C385" s="94"/>
+      <c r="C385" s="92"/>
     </row>
     <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C386" s="94"/>
+      <c r="C386" s="92"/>
     </row>
     <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C387" s="94"/>
+      <c r="C387" s="92"/>
     </row>
     <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C388" s="94"/>
+      <c r="C388" s="92"/>
     </row>
     <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C389" s="94"/>
+      <c r="C389" s="92"/>
     </row>
     <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C390" s="94"/>
+      <c r="C390" s="92"/>
     </row>
     <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C391" s="94"/>
+      <c r="C391" s="92"/>
     </row>
     <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C392" s="94"/>
+      <c r="C392" s="92"/>
     </row>
     <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C393" s="94"/>
+      <c r="C393" s="92"/>
     </row>
     <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C394" s="94"/>
+      <c r="C394" s="92"/>
     </row>
     <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C395" s="94"/>
+      <c r="C395" s="92"/>
     </row>
     <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C396" s="94"/>
+      <c r="C396" s="92"/>
     </row>
     <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C397" s="94"/>
+      <c r="C397" s="92"/>
     </row>
     <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C398" s="94"/>
+      <c r="C398" s="92"/>
     </row>
     <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C399" s="94"/>
+      <c r="C399" s="92"/>
     </row>
     <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C400" s="94"/>
+      <c r="C400" s="92"/>
     </row>
     <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C401" s="94"/>
+      <c r="C401" s="92"/>
     </row>
     <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C402" s="94"/>
+      <c r="C402" s="92"/>
     </row>
     <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C403" s="94"/>
+      <c r="C403" s="92"/>
     </row>
     <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C404" s="94"/>
+      <c r="C404" s="92"/>
     </row>
     <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C405" s="94"/>
+      <c r="C405" s="92"/>
     </row>
     <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C406" s="94"/>
+      <c r="C406" s="92"/>
     </row>
     <row r="407" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C407" s="94"/>
+      <c r="C407" s="92"/>
     </row>
     <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C408" s="94"/>
+      <c r="C408" s="92"/>
     </row>
     <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C409" s="94"/>
+      <c r="C409" s="92"/>
     </row>
     <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C410" s="94"/>
+      <c r="C410" s="92"/>
     </row>
     <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C411" s="94"/>
+      <c r="C411" s="92"/>
     </row>
     <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C412" s="94"/>
+      <c r="C412" s="92"/>
     </row>
     <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C413" s="94"/>
+      <c r="C413" s="92"/>
     </row>
     <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C414" s="94"/>
+      <c r="C414" s="92"/>
     </row>
     <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C415" s="94"/>
+      <c r="C415" s="92"/>
     </row>
     <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C416" s="94"/>
+      <c r="C416" s="92"/>
     </row>
     <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C417" s="94"/>
+      <c r="C417" s="92"/>
     </row>
     <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C418" s="94"/>
+      <c r="C418" s="92"/>
     </row>
     <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C419" s="94"/>
+      <c r="C419" s="92"/>
     </row>
     <row r="420" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C420" s="94"/>
+      <c r="C420" s="92"/>
     </row>
     <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C421" s="94"/>
+      <c r="C421" s="92"/>
     </row>
     <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C422" s="94"/>
+      <c r="C422" s="92"/>
     </row>
     <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C423" s="94"/>
+      <c r="C423" s="92"/>
     </row>
     <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C424" s="94"/>
+      <c r="C424" s="92"/>
     </row>
     <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C425" s="94"/>
+      <c r="C425" s="92"/>
     </row>
     <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C426" s="94"/>
+      <c r="C426" s="92"/>
     </row>
     <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C427" s="94"/>
+      <c r="C427" s="92"/>
     </row>
     <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C428" s="94"/>
+      <c r="C428" s="92"/>
     </row>
     <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C429" s="94"/>
+      <c r="C429" s="92"/>
     </row>
     <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C430" s="94"/>
+      <c r="C430" s="92"/>
     </row>
     <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C431" s="94"/>
+      <c r="C431" s="92"/>
     </row>
     <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C432" s="94"/>
+      <c r="C432" s="92"/>
     </row>
     <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C433" s="94"/>
+      <c r="C433" s="92"/>
     </row>
     <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C434" s="94"/>
+      <c r="C434" s="92"/>
     </row>
     <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C435" s="94"/>
+      <c r="C435" s="92"/>
     </row>
     <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C436" s="94"/>
+      <c r="C436" s="92"/>
     </row>
     <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C437" s="94"/>
+      <c r="C437" s="92"/>
     </row>
     <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C438" s="94"/>
+      <c r="C438" s="92"/>
     </row>
     <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C439" s="94"/>
+      <c r="C439" s="92"/>
     </row>
     <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C440" s="94"/>
+      <c r="C440" s="92"/>
     </row>
     <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C441" s="94"/>
+      <c r="C441" s="92"/>
     </row>
     <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C442" s="94"/>
+      <c r="C442" s="92"/>
     </row>
     <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C443" s="94"/>
+      <c r="C443" s="92"/>
     </row>
     <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C444" s="94"/>
+      <c r="C444" s="92"/>
     </row>
     <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C445" s="94"/>
+      <c r="C445" s="92"/>
     </row>
     <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C446" s="94"/>
+      <c r="C446" s="92"/>
     </row>
     <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C447" s="94"/>
+      <c r="C447" s="92"/>
     </row>
     <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C448" s="94"/>
+      <c r="C448" s="92"/>
     </row>
     <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C449" s="94"/>
+      <c r="C449" s="92"/>
     </row>
     <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C450" s="94"/>
+      <c r="C450" s="92"/>
     </row>
     <row r="451" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C451" s="94"/>
+      <c r="C451" s="92"/>
     </row>
     <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C452" s="94"/>
+      <c r="C452" s="92"/>
     </row>
     <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C453" s="94"/>
+      <c r="C453" s="92"/>
     </row>
     <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C454" s="94"/>
+      <c r="C454" s="92"/>
     </row>
     <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C455" s="94"/>
+      <c r="C455" s="92"/>
     </row>
     <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C456" s="94"/>
+      <c r="C456" s="92"/>
     </row>
     <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C457" s="94"/>
+      <c r="C457" s="92"/>
     </row>
     <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C458" s="94"/>
+      <c r="C458" s="92"/>
     </row>
     <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C459" s="94"/>
+      <c r="C459" s="92"/>
     </row>
     <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C460" s="94"/>
+      <c r="C460" s="92"/>
     </row>
     <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C461" s="94"/>
+      <c r="C461" s="92"/>
     </row>
     <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C462" s="94"/>
+      <c r="C462" s="92"/>
     </row>
     <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C463" s="94"/>
+      <c r="C463" s="92"/>
     </row>
     <row r="464" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C464" s="94"/>
+      <c r="C464" s="92"/>
     </row>
     <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C465" s="94"/>
+      <c r="C465" s="92"/>
     </row>
     <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C466" s="94"/>
+      <c r="C466" s="92"/>
     </row>
     <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C467" s="94"/>
+      <c r="C467" s="92"/>
     </row>
     <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C468" s="94"/>
+      <c r="C468" s="92"/>
     </row>
     <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C469" s="94"/>
+      <c r="C469" s="92"/>
     </row>
     <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C470" s="94"/>
+      <c r="C470" s="92"/>
     </row>
     <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C471" s="94"/>
+      <c r="C471" s="92"/>
     </row>
     <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C472" s="94"/>
+      <c r="C472" s="92"/>
     </row>
     <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C473" s="94"/>
+      <c r="C473" s="92"/>
     </row>
     <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C474" s="94"/>
+      <c r="C474" s="92"/>
     </row>
     <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C475" s="94"/>
+      <c r="C475" s="92"/>
     </row>
     <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C476" s="94"/>
+      <c r="C476" s="92"/>
     </row>
     <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C477" s="94"/>
+      <c r="C477" s="92"/>
     </row>
     <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C478" s="94"/>
+      <c r="C478" s="92"/>
     </row>
     <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C479" s="94"/>
+      <c r="C479" s="92"/>
     </row>
     <row r="480" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C480" s="94"/>
+      <c r="C480" s="92"/>
     </row>
     <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C481" s="94"/>
+      <c r="C481" s="92"/>
     </row>
     <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C482" s="94"/>
+      <c r="C482" s="92"/>
     </row>
     <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C483" s="94"/>
+      <c r="C483" s="92"/>
     </row>
     <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C484" s="94"/>
+      <c r="C484" s="92"/>
     </row>
     <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C485" s="94"/>
+      <c r="C485" s="92"/>
     </row>
     <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C486" s="94"/>
+      <c r="C486" s="92"/>
     </row>
     <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C487" s="94"/>
+      <c r="C487" s="92"/>
     </row>
     <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C488" s="94"/>
+      <c r="C488" s="92"/>
     </row>
     <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C489" s="94"/>
+      <c r="C489" s="92"/>
     </row>
     <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C490" s="94"/>
+      <c r="C490" s="92"/>
     </row>
     <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C491" s="94"/>
+      <c r="C491" s="92"/>
     </row>
     <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C492" s="94"/>
+      <c r="C492" s="92"/>
     </row>
     <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C493" s="94"/>
+      <c r="C493" s="92"/>
     </row>
     <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C494" s="94"/>
+      <c r="C494" s="92"/>
     </row>
     <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C495" s="94"/>
+      <c r="C495" s="92"/>
     </row>
     <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C496" s="94"/>
+      <c r="C496" s="92"/>
     </row>
     <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C497" s="94"/>
+      <c r="C497" s="92"/>
     </row>
     <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C498" s="94"/>
+      <c r="C498" s="92"/>
     </row>
     <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C499" s="94"/>
+      <c r="C499" s="92"/>
     </row>
     <row r="500" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C500" s="94"/>
+      <c r="C500" s="92"/>
     </row>
     <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C501" s="94"/>
+      <c r="C501" s="92"/>
     </row>
     <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C502" s="94"/>
+      <c r="C502" s="92"/>
     </row>
     <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C503" s="94"/>
+      <c r="C503" s="92"/>
     </row>
     <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C504" s="94"/>
+      <c r="C504" s="92"/>
     </row>
     <row r="505" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C505" s="94"/>
+      <c r="C505" s="92"/>
     </row>
     <row r="506" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C506" s="94"/>
+      <c r="C506" s="92"/>
     </row>
     <row r="507" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C507" s="94"/>
+      <c r="C507" s="92"/>
     </row>
     <row r="508" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C508" s="94"/>
+      <c r="C508" s="92"/>
     </row>
     <row r="509" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C509" s="94"/>
+      <c r="C509" s="92"/>
     </row>
     <row r="510" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C510" s="94"/>
+      <c r="C510" s="92"/>
     </row>
     <row r="511" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C511" s="94"/>
+      <c r="C511" s="92"/>
     </row>
     <row r="512" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C512" s="94"/>
+      <c r="C512" s="92"/>
     </row>
     <row r="513" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C513" s="94"/>
+      <c r="C513" s="92"/>
     </row>
     <row r="514" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C514" s="94"/>
+      <c r="C514" s="92"/>
     </row>
     <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C515" s="94"/>
+      <c r="C515" s="92"/>
     </row>
     <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C516" s="94"/>
+      <c r="C516" s="92"/>
     </row>
     <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C517" s="94"/>
+      <c r="C517" s="92"/>
     </row>
     <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C518" s="94"/>
+      <c r="C518" s="92"/>
     </row>
     <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C519" s="94"/>
+      <c r="C519" s="92"/>
     </row>
     <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C520" s="94"/>
+      <c r="C520" s="92"/>
     </row>
     <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C521" s="94"/>
+      <c r="C521" s="92"/>
     </row>
     <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C522" s="94"/>
+      <c r="C522" s="92"/>
     </row>
     <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C523" s="94"/>
+      <c r="C523" s="92"/>
     </row>
     <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C524" s="94"/>
+      <c r="C524" s="92"/>
     </row>
     <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C525" s="94"/>
+      <c r="C525" s="92"/>
     </row>
     <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C526" s="94"/>
+      <c r="C526" s="92"/>
     </row>
     <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C527" s="94"/>
+      <c r="C527" s="92"/>
     </row>
     <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C528" s="94"/>
+      <c r="C528" s="92"/>
     </row>
     <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C529" s="94"/>
+      <c r="C529" s="92"/>
     </row>
     <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C530" s="94"/>
+      <c r="C530" s="92"/>
     </row>
     <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C531" s="94"/>
+      <c r="C531" s="92"/>
     </row>
     <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C532" s="94"/>
+      <c r="C532" s="92"/>
     </row>
     <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C533" s="94"/>
+      <c r="C533" s="92"/>
     </row>
     <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C534" s="94"/>
+      <c r="C534" s="92"/>
     </row>
     <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C535" s="94"/>
+      <c r="C535" s="92"/>
     </row>
     <row r="536" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C536" s="94"/>
+      <c r="C536" s="92"/>
     </row>
     <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C537" s="94"/>
+      <c r="C537" s="92"/>
     </row>
     <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C538" s="94"/>
+      <c r="C538" s="92"/>
     </row>
     <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C539" s="94"/>
+      <c r="C539" s="92"/>
     </row>
     <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C540" s="94"/>
+      <c r="C540" s="92"/>
     </row>
     <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C541" s="94"/>
+      <c r="C541" s="92"/>
     </row>
     <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C542" s="94"/>
+      <c r="C542" s="92"/>
     </row>
     <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C543" s="94"/>
+      <c r="C543" s="92"/>
     </row>
     <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C544" s="94"/>
+      <c r="C544" s="92"/>
     </row>
     <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C545" s="94"/>
+      <c r="C545" s="92"/>
     </row>
     <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C546" s="94"/>
+      <c r="C546" s="92"/>
     </row>
     <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C547" s="94"/>
+      <c r="C547" s="92"/>
     </row>
     <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C548" s="94"/>
+      <c r="C548" s="92"/>
     </row>
     <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C549" s="94"/>
+      <c r="C549" s="92"/>
     </row>
     <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C550" s="94"/>
+      <c r="C550" s="92"/>
     </row>
     <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C551" s="94"/>
+      <c r="C551" s="92"/>
     </row>
     <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C552" s="94"/>
+      <c r="C552" s="92"/>
     </row>
     <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C553" s="94"/>
+      <c r="C553" s="92"/>
     </row>
     <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C554" s="94"/>
+      <c r="C554" s="92"/>
     </row>
     <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C555" s="94"/>
+      <c r="C555" s="92"/>
     </row>
     <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C556" s="94"/>
+      <c r="C556" s="92"/>
     </row>
     <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C557" s="94"/>
+      <c r="C557" s="92"/>
     </row>
     <row r="558" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C558" s="94"/>
+      <c r="C558" s="92"/>
     </row>
     <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C559" s="94"/>
+      <c r="C559" s="92"/>
     </row>
     <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C560" s="94"/>
+      <c r="C560" s="92"/>
     </row>
     <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C561" s="94"/>
+      <c r="C561" s="92"/>
     </row>
     <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C562" s="94"/>
+      <c r="C562" s="92"/>
     </row>
     <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C563" s="94"/>
+      <c r="C563" s="92"/>
     </row>
     <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C564" s="94"/>
+      <c r="C564" s="92"/>
     </row>
     <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C565" s="94"/>
+      <c r="C565" s="92"/>
     </row>
     <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C566" s="94"/>
+      <c r="C566" s="92"/>
     </row>
     <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C567" s="94"/>
+      <c r="C567" s="92"/>
     </row>
     <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C568" s="94"/>
+      <c r="C568" s="92"/>
     </row>
     <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C569" s="94"/>
+      <c r="C569" s="92"/>
     </row>
     <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C570" s="94"/>
+      <c r="C570" s="92"/>
     </row>
     <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C571" s="94"/>
+      <c r="C571" s="92"/>
     </row>
     <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C572" s="94"/>
+      <c r="C572" s="92"/>
     </row>
     <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C573" s="94"/>
+      <c r="C573" s="92"/>
     </row>
     <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C574" s="94"/>
+      <c r="C574" s="92"/>
     </row>
     <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C575" s="94"/>
+      <c r="C575" s="92"/>
     </row>
     <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C576" s="94"/>
+      <c r="C576" s="92"/>
     </row>
     <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C577" s="94"/>
+      <c r="C577" s="92"/>
     </row>
     <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C578" s="94"/>
+      <c r="C578" s="92"/>
     </row>
     <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C579" s="94"/>
+      <c r="C579" s="92"/>
     </row>
     <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C580" s="94"/>
+      <c r="C580" s="92"/>
     </row>
     <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C581" s="94"/>
+      <c r="C581" s="92"/>
     </row>
     <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C582" s="94"/>
+      <c r="C582" s="92"/>
     </row>
     <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C583" s="94"/>
+      <c r="C583" s="92"/>
     </row>
     <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C584" s="94"/>
+      <c r="C584" s="92"/>
     </row>
     <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C585" s="94"/>
+      <c r="C585" s="92"/>
     </row>
     <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C586" s="94"/>
+      <c r="C586" s="92"/>
     </row>
     <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C587" s="94"/>
+      <c r="C587" s="92"/>
     </row>
     <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C588" s="94"/>
+      <c r="C588" s="92"/>
     </row>
     <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C589" s="94"/>
+      <c r="C589" s="92"/>
     </row>
     <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C590" s="94"/>
+      <c r="C590" s="92"/>
     </row>
     <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C591" s="94"/>
+      <c r="C591" s="92"/>
     </row>
     <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C592" s="94"/>
+      <c r="C592" s="92"/>
     </row>
     <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C593" s="94"/>
+      <c r="C593" s="92"/>
     </row>
     <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C594" s="94"/>
+      <c r="C594" s="92"/>
     </row>
     <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C595" s="94"/>
+      <c r="C595" s="92"/>
     </row>
     <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C596" s="94"/>
+      <c r="C596" s="92"/>
     </row>
     <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C597" s="94"/>
+      <c r="C597" s="92"/>
     </row>
     <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C598" s="94"/>
+      <c r="C598" s="92"/>
     </row>
     <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C599" s="94"/>
+      <c r="C599" s="92"/>
     </row>
     <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C600" s="94"/>
+      <c r="C600" s="92"/>
     </row>
     <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C601" s="94"/>
+      <c r="C601" s="92"/>
     </row>
     <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C602" s="94"/>
+      <c r="C602" s="92"/>
     </row>
     <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C603" s="94"/>
+      <c r="C603" s="92"/>
     </row>
     <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C604" s="94"/>
+      <c r="C604" s="92"/>
     </row>
     <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C605" s="94"/>
+      <c r="C605" s="92"/>
     </row>
     <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C606" s="94"/>
+      <c r="C606" s="92"/>
     </row>
     <row r="607" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C607" s="94"/>
+      <c r="C607" s="92"/>
     </row>
     <row r="608" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C608" s="94"/>
+      <c r="C608" s="92"/>
     </row>
     <row r="609" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C609" s="94"/>
+      <c r="C609" s="92"/>
     </row>
     <row r="610" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C610" s="94"/>
+      <c r="C610" s="92"/>
     </row>
     <row r="611" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C611" s="94"/>
+      <c r="C611" s="92"/>
     </row>
     <row r="612" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C612" s="94"/>
+      <c r="C612" s="92"/>
     </row>
     <row r="613" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C613" s="94"/>
+      <c r="C613" s="92"/>
     </row>
     <row r="614" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C614" s="94"/>
+      <c r="C614" s="92"/>
     </row>
     <row r="615" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C615" s="94"/>
+      <c r="C615" s="92"/>
     </row>
     <row r="616" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C616" s="94"/>
+      <c r="C616" s="92"/>
     </row>
     <row r="617" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C617" s="94"/>
+      <c r="C617" s="92"/>
     </row>
     <row r="618" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C618" s="94"/>
+      <c r="C618" s="92"/>
     </row>
     <row r="619" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C619" s="94"/>
+      <c r="C619" s="92"/>
     </row>
     <row r="620" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C620" s="94"/>
+      <c r="C620" s="92"/>
     </row>
     <row r="621" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C621" s="94"/>
+      <c r="C621" s="92"/>
     </row>
     <row r="622" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C622" s="94"/>
+      <c r="C622" s="92"/>
     </row>
     <row r="623" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C623" s="94"/>
+      <c r="C623" s="92"/>
     </row>
     <row r="624" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C624" s="94"/>
+      <c r="C624" s="92"/>
     </row>
     <row r="625" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C625" s="94"/>
+      <c r="C625" s="92"/>
     </row>
     <row r="626" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C626" s="94"/>
+      <c r="C626" s="92"/>
     </row>
     <row r="627" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C627" s="94"/>
+      <c r="C627" s="92"/>
     </row>
     <row r="628" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C628" s="94"/>
+      <c r="C628" s="92"/>
     </row>
     <row r="629" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C629" s="94"/>
+      <c r="C629" s="92"/>
     </row>
     <row r="630" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C630" s="94"/>
+      <c r="C630" s="92"/>
     </row>
     <row r="631" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C631" s="94"/>
+      <c r="C631" s="92"/>
     </row>
     <row r="632" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C632" s="94"/>
+      <c r="C632" s="92"/>
     </row>
     <row r="633" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C633" s="94"/>
+      <c r="C633" s="92"/>
     </row>
     <row r="634" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C634" s="94"/>
+      <c r="C634" s="92"/>
     </row>
     <row r="635" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C635" s="94"/>
+      <c r="C635" s="92"/>
     </row>
     <row r="636" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C636" s="94"/>
+      <c r="C636" s="92"/>
     </row>
     <row r="637" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C637" s="94"/>
+      <c r="C637" s="92"/>
     </row>
     <row r="638" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C638" s="94"/>
+      <c r="C638" s="92"/>
     </row>
     <row r="639" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C639" s="94"/>
+      <c r="C639" s="92"/>
     </row>
     <row r="640" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C640" s="94"/>
+      <c r="C640" s="92"/>
     </row>
     <row r="641" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C641" s="94"/>
+      <c r="C641" s="92"/>
     </row>
     <row r="642" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C642" s="94"/>
+      <c r="C642" s="92"/>
     </row>
     <row r="643" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C643" s="94"/>
+      <c r="C643" s="92"/>
     </row>
     <row r="644" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C644" s="94"/>
+      <c r="C644" s="92"/>
     </row>
     <row r="645" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C645" s="94"/>
+      <c r="C645" s="92"/>
     </row>
     <row r="646" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C646" s="94"/>
+      <c r="C646" s="92"/>
     </row>
     <row r="647" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C647" s="94"/>
+      <c r="C647" s="92"/>
     </row>
     <row r="648" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C648" s="94"/>
+      <c r="C648" s="92"/>
     </row>
     <row r="649" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C649" s="94"/>
+      <c r="C649" s="92"/>
     </row>
     <row r="650" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C650" s="94"/>
+      <c r="C650" s="92"/>
     </row>
     <row r="651" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C651" s="94"/>
+      <c r="C651" s="92"/>
     </row>
     <row r="652" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C652" s="94"/>
+      <c r="C652" s="92"/>
     </row>
     <row r="653" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C653" s="94"/>
+      <c r="C653" s="92"/>
     </row>
     <row r="654" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C654" s="94"/>
+      <c r="C654" s="92"/>
     </row>
     <row r="655" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C655" s="94"/>
+      <c r="C655" s="92"/>
     </row>
     <row r="656" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C656" s="94"/>
+      <c r="C656" s="92"/>
     </row>
     <row r="657" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C657" s="94"/>
+      <c r="C657" s="92"/>
     </row>
     <row r="658" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C658" s="94"/>
+      <c r="C658" s="92"/>
     </row>
     <row r="659" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C659" s="94"/>
+      <c r="C659" s="92"/>
     </row>
     <row r="660" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C660" s="94"/>
+      <c r="C660" s="92"/>
     </row>
     <row r="661" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C661" s="94"/>
+      <c r="C661" s="92"/>
     </row>
     <row r="662" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C662" s="94"/>
+      <c r="C662" s="92"/>
     </row>
     <row r="663" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C663" s="94"/>
+      <c r="C663" s="92"/>
     </row>
     <row r="664" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C664" s="94"/>
+      <c r="C664" s="92"/>
     </row>
     <row r="665" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C665" s="94"/>
+      <c r="C665" s="92"/>
     </row>
     <row r="666" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C666" s="94"/>
+      <c r="C666" s="92"/>
     </row>
     <row r="667" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C667" s="94"/>
+      <c r="C667" s="92"/>
     </row>
     <row r="668" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C668" s="94"/>
+      <c r="C668" s="92"/>
     </row>
     <row r="669" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C669" s="94"/>
+      <c r="C669" s="92"/>
     </row>
     <row r="670" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C670" s="94"/>
+      <c r="C670" s="92"/>
     </row>
     <row r="671" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C671" s="94"/>
+      <c r="C671" s="92"/>
     </row>
     <row r="672" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C672" s="94"/>
+      <c r="C672" s="92"/>
     </row>
     <row r="673" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C673" s="94"/>
+      <c r="C673" s="92"/>
     </row>
     <row r="674" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C674" s="94"/>
+      <c r="C674" s="92"/>
     </row>
     <row r="675" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C675" s="94"/>
+      <c r="C675" s="92"/>
     </row>
     <row r="676" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C676" s="94"/>
+      <c r="C676" s="92"/>
     </row>
     <row r="677" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C677" s="94"/>
+      <c r="C677" s="92"/>
     </row>
     <row r="678" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C678" s="94"/>
+      <c r="C678" s="92"/>
     </row>
     <row r="679" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C679" s="94"/>
+      <c r="C679" s="92"/>
     </row>
     <row r="680" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C680" s="94"/>
+      <c r="C680" s="92"/>
     </row>
     <row r="681" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C681" s="94"/>
+      <c r="C681" s="92"/>
     </row>
     <row r="682" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C682" s="94"/>
+      <c r="C682" s="92"/>
     </row>
     <row r="683" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C683" s="94"/>
+      <c r="C683" s="92"/>
     </row>
     <row r="684" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C684" s="94"/>
+      <c r="C684" s="92"/>
     </row>
     <row r="685" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C685" s="94"/>
+      <c r="C685" s="92"/>
     </row>
     <row r="686" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C686" s="94"/>
+      <c r="C686" s="92"/>
     </row>
     <row r="687" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C687" s="94"/>
+      <c r="C687" s="92"/>
     </row>
     <row r="688" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C688" s="94"/>
+      <c r="C688" s="92"/>
     </row>
     <row r="689" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C689" s="94"/>
+      <c r="C689" s="92"/>
     </row>
     <row r="690" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C690" s="94"/>
+      <c r="C690" s="92"/>
     </row>
     <row r="691" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C691" s="94"/>
+      <c r="C691" s="92"/>
     </row>
     <row r="692" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C692" s="94"/>
+      <c r="C692" s="92"/>
     </row>
     <row r="693" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C693" s="94"/>
+      <c r="C693" s="92"/>
     </row>
     <row r="694" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C694" s="94"/>
+      <c r="C694" s="92"/>
     </row>
     <row r="695" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C695" s="94"/>
+      <c r="C695" s="92"/>
     </row>
     <row r="696" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C696" s="94"/>
+      <c r="C696" s="92"/>
     </row>
     <row r="697" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C697" s="94"/>
+      <c r="C697" s="92"/>
     </row>
     <row r="698" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C698" s="94"/>
+      <c r="C698" s="92"/>
     </row>
     <row r="699" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C699" s="94"/>
+      <c r="C699" s="92"/>
     </row>
     <row r="700" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C700" s="94"/>
+      <c r="C700" s="92"/>
     </row>
     <row r="701" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C701" s="94"/>
+      <c r="C701" s="92"/>
     </row>
     <row r="702" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C702" s="94"/>
+      <c r="C702" s="92"/>
     </row>
     <row r="703" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C703" s="94"/>
+      <c r="C703" s="92"/>
     </row>
     <row r="704" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C704" s="94"/>
+      <c r="C704" s="92"/>
     </row>
     <row r="705" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C705" s="94"/>
+      <c r="C705" s="92"/>
     </row>
     <row r="706" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C706" s="94"/>
+      <c r="C706" s="92"/>
     </row>
     <row r="707" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C707" s="94"/>
+      <c r="C707" s="92"/>
     </row>
     <row r="708" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C708" s="94"/>
+      <c r="C708" s="92"/>
     </row>
     <row r="709" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C709" s="94"/>
+      <c r="C709" s="92"/>
     </row>
     <row r="710" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C710" s="94"/>
+      <c r="C710" s="92"/>
     </row>
     <row r="711" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C711" s="94"/>
+      <c r="C711" s="92"/>
     </row>
     <row r="712" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C712" s="94"/>
+      <c r="C712" s="92"/>
     </row>
     <row r="713" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C713" s="94"/>
+      <c r="C713" s="92"/>
     </row>
     <row r="714" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C714" s="94"/>
+      <c r="C714" s="92"/>
     </row>
     <row r="715" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C715" s="94"/>
+      <c r="C715" s="92"/>
     </row>
     <row r="716" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C716" s="94"/>
+      <c r="C716" s="92"/>
     </row>
     <row r="717" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C717" s="94"/>
+      <c r="C717" s="92"/>
     </row>
     <row r="718" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C718" s="94"/>
+      <c r="C718" s="92"/>
     </row>
     <row r="719" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C719" s="94"/>
+      <c r="C719" s="92"/>
     </row>
     <row r="720" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C720" s="94"/>
+      <c r="C720" s="92"/>
     </row>
     <row r="721" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C721" s="94"/>
+      <c r="C721" s="92"/>
     </row>
     <row r="722" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C722" s="94"/>
+      <c r="C722" s="92"/>
     </row>
     <row r="723" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C723" s="94"/>
+      <c r="C723" s="92"/>
     </row>
     <row r="724" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C724" s="94"/>
+      <c r="C724" s="92"/>
     </row>
     <row r="725" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C725" s="94"/>
+      <c r="C725" s="92"/>
     </row>
     <row r="726" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C726" s="94"/>
+      <c r="C726" s="92"/>
     </row>
     <row r="727" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C727" s="94"/>
+      <c r="C727" s="92"/>
     </row>
     <row r="728" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C728" s="94"/>
+      <c r="C728" s="92"/>
     </row>
     <row r="729" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C729" s="94"/>
+      <c r="C729" s="92"/>
     </row>
     <row r="730" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C730" s="94"/>
+      <c r="C730" s="92"/>
     </row>
     <row r="731" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C731" s="94"/>
+      <c r="C731" s="92"/>
     </row>
     <row r="732" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C732" s="94"/>
+      <c r="C732" s="92"/>
     </row>
     <row r="733" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C733" s="94"/>
+      <c r="C733" s="92"/>
     </row>
     <row r="734" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C734" s="94"/>
+      <c r="C734" s="92"/>
     </row>
     <row r="735" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C735" s="94"/>
+      <c r="C735" s="92"/>
     </row>
     <row r="736" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C736" s="94"/>
+      <c r="C736" s="92"/>
     </row>
     <row r="737" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C737" s="94"/>
+      <c r="C737" s="92"/>
     </row>
     <row r="738" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C738" s="94"/>
+      <c r="C738" s="92"/>
     </row>
     <row r="739" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C739" s="94"/>
+      <c r="C739" s="92"/>
     </row>
     <row r="740" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C740" s="94"/>
+      <c r="C740" s="92"/>
     </row>
     <row r="741" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C741" s="94"/>
+      <c r="C741" s="92"/>
     </row>
     <row r="742" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C742" s="94"/>
+      <c r="C742" s="92"/>
     </row>
     <row r="743" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C743" s="94"/>
+      <c r="C743" s="92"/>
     </row>
     <row r="744" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C744" s="94"/>
+      <c r="C744" s="92"/>
     </row>
     <row r="745" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C745" s="94"/>
+      <c r="C745" s="92"/>
     </row>
     <row r="746" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C746" s="94"/>
+      <c r="C746" s="92"/>
     </row>
     <row r="747" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C747" s="94"/>
+      <c r="C747" s="92"/>
     </row>
     <row r="748" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C748" s="94"/>
+      <c r="C748" s="92"/>
     </row>
     <row r="749" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C749" s="94"/>
+      <c r="C749" s="92"/>
     </row>
     <row r="750" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C750" s="94"/>
+      <c r="C750" s="92"/>
     </row>
     <row r="751" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C751" s="94"/>
+      <c r="C751" s="92"/>
     </row>
     <row r="752" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C752" s="94"/>
+      <c r="C752" s="92"/>
     </row>
     <row r="753" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C753" s="94"/>
+      <c r="C753" s="92"/>
     </row>
     <row r="754" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C754" s="94"/>
+      <c r="C754" s="92"/>
     </row>
     <row r="755" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C755" s="94"/>
+      <c r="C755" s="92"/>
     </row>
     <row r="756" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C756" s="94"/>
+      <c r="C756" s="92"/>
     </row>
     <row r="757" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C757" s="94"/>
+      <c r="C757" s="92"/>
     </row>
     <row r="758" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C758" s="94"/>
+      <c r="C758" s="92"/>
     </row>
     <row r="759" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C759" s="94"/>
+      <c r="C759" s="92"/>
     </row>
     <row r="760" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C760" s="94"/>
+      <c r="C760" s="92"/>
     </row>
     <row r="761" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C761" s="94"/>
+      <c r="C761" s="92"/>
     </row>
     <row r="762" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C762" s="94"/>
+      <c r="C762" s="92"/>
     </row>
     <row r="763" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C763" s="94"/>
+      <c r="C763" s="92"/>
     </row>
     <row r="764" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C764" s="94"/>
+      <c r="C764" s="92"/>
     </row>
     <row r="765" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C765" s="94"/>
+      <c r="C765" s="92"/>
     </row>
     <row r="766" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C766" s="94"/>
+      <c r="C766" s="92"/>
     </row>
     <row r="767" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C767" s="94"/>
+      <c r="C767" s="92"/>
     </row>
     <row r="768" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C768" s="94"/>
+      <c r="C768" s="92"/>
     </row>
     <row r="769" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C769" s="94"/>
+      <c r="C769" s="92"/>
     </row>
     <row r="770" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C770" s="94"/>
+      <c r="C770" s="92"/>
     </row>
     <row r="771" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C771" s="94"/>
+      <c r="C771" s="92"/>
     </row>
     <row r="772" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C772" s="94"/>
+      <c r="C772" s="92"/>
     </row>
     <row r="773" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C773" s="94"/>
+      <c r="C773" s="92"/>
     </row>
     <row r="774" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C774" s="94"/>
+      <c r="C774" s="92"/>
     </row>
     <row r="775" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C775" s="94"/>
+      <c r="C775" s="92"/>
     </row>
     <row r="776" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C776" s="94"/>
+      <c r="C776" s="92"/>
     </row>
     <row r="777" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C777" s="94"/>
+      <c r="C777" s="92"/>
     </row>
     <row r="778" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C778" s="94"/>
+      <c r="C778" s="92"/>
     </row>
     <row r="779" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C779" s="94"/>
+      <c r="C779" s="92"/>
     </row>
     <row r="780" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C780" s="94"/>
+      <c r="C780" s="92"/>
     </row>
     <row r="781" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C781" s="94"/>
+      <c r="C781" s="92"/>
     </row>
     <row r="782" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C782" s="94"/>
+      <c r="C782" s="92"/>
     </row>
     <row r="783" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C783" s="94"/>
+      <c r="C783" s="92"/>
     </row>
     <row r="784" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C784" s="94"/>
+      <c r="C784" s="92"/>
     </row>
     <row r="785" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C785" s="94"/>
+      <c r="C785" s="92"/>
     </row>
     <row r="786" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C786" s="94"/>
+      <c r="C786" s="92"/>
     </row>
     <row r="787" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C787" s="94"/>
+      <c r="C787" s="92"/>
     </row>
     <row r="788" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C788" s="94"/>
+      <c r="C788" s="92"/>
     </row>
     <row r="789" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C789" s="94"/>
+      <c r="C789" s="92"/>
     </row>
     <row r="790" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C790" s="94"/>
+      <c r="C790" s="92"/>
     </row>
     <row r="791" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C791" s="94"/>
+      <c r="C791" s="92"/>
     </row>
     <row r="792" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C792" s="94"/>
+      <c r="C792" s="92"/>
     </row>
     <row r="793" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C793" s="94"/>
+      <c r="C793" s="92"/>
     </row>
     <row r="794" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C794" s="94"/>
+      <c r="C794" s="92"/>
     </row>
     <row r="795" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C795" s="94"/>
+      <c r="C795" s="92"/>
     </row>
     <row r="796" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C796" s="94"/>
+      <c r="C796" s="92"/>
     </row>
     <row r="797" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C797" s="94"/>
+      <c r="C797" s="92"/>
     </row>
     <row r="798" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C798" s="94"/>
+      <c r="C798" s="92"/>
     </row>
     <row r="799" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C799" s="94"/>
+      <c r="C799" s="92"/>
     </row>
     <row r="800" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C800" s="94"/>
+      <c r="C800" s="92"/>
     </row>
     <row r="801" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C801" s="94"/>
+      <c r="C801" s="92"/>
     </row>
     <row r="802" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C802" s="94"/>
+      <c r="C802" s="92"/>
     </row>
     <row r="803" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C803" s="94"/>
+      <c r="C803" s="92"/>
     </row>
     <row r="804" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C804" s="94"/>
+      <c r="C804" s="92"/>
     </row>
     <row r="805" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C805" s="94"/>
+      <c r="C805" s="92"/>
     </row>
     <row r="806" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C806" s="94"/>
+      <c r="C806" s="92"/>
     </row>
     <row r="807" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C807" s="94"/>
+      <c r="C807" s="92"/>
     </row>
     <row r="808" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C808" s="94"/>
+      <c r="C808" s="92"/>
     </row>
     <row r="809" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C809" s="94"/>
+      <c r="C809" s="92"/>
     </row>
     <row r="810" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C810" s="94"/>
+      <c r="C810" s="92"/>
     </row>
     <row r="811" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C811" s="94"/>
+      <c r="C811" s="92"/>
     </row>
     <row r="812" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C812" s="94"/>
+      <c r="C812" s="92"/>
     </row>
     <row r="813" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C813" s="94"/>
+      <c r="C813" s="92"/>
     </row>
     <row r="814" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C814" s="94"/>
+      <c r="C814" s="92"/>
     </row>
     <row r="815" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C815" s="94"/>
+      <c r="C815" s="92"/>
     </row>
     <row r="816" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C816" s="94"/>
+      <c r="C816" s="92"/>
     </row>
     <row r="817" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C817" s="94"/>
+      <c r="C817" s="92"/>
     </row>
     <row r="818" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C818" s="94"/>
+      <c r="C818" s="92"/>
     </row>
     <row r="819" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C819" s="94"/>
+      <c r="C819" s="92"/>
     </row>
     <row r="820" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C820" s="94"/>
+      <c r="C820" s="92"/>
     </row>
     <row r="821" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C821" s="94"/>
+      <c r="C821" s="92"/>
     </row>
     <row r="822" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C822" s="94"/>
+      <c r="C822" s="92"/>
     </row>
     <row r="823" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C823" s="94"/>
+      <c r="C823" s="92"/>
     </row>
     <row r="824" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C824" s="94"/>
+      <c r="C824" s="92"/>
     </row>
     <row r="825" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C825" s="94"/>
+      <c r="C825" s="92"/>
     </row>
     <row r="826" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C826" s="94"/>
+      <c r="C826" s="92"/>
     </row>
     <row r="827" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C827" s="94"/>
+      <c r="C827" s="92"/>
     </row>
     <row r="828" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C828" s="94"/>
+      <c r="C828" s="92"/>
     </row>
     <row r="829" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C829" s="94"/>
+      <c r="C829" s="92"/>
     </row>
     <row r="830" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C830" s="94"/>
+      <c r="C830" s="92"/>
     </row>
     <row r="831" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C831" s="94"/>
+      <c r="C831" s="92"/>
     </row>
     <row r="832" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C832" s="94"/>
+      <c r="C832" s="92"/>
     </row>
     <row r="833" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C833" s="94"/>
+      <c r="C833" s="92"/>
     </row>
     <row r="834" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C834" s="94"/>
+      <c r="C834" s="92"/>
     </row>
     <row r="835" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C835" s="94"/>
+      <c r="C835" s="92"/>
     </row>
     <row r="836" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C836" s="94"/>
+      <c r="C836" s="92"/>
     </row>
     <row r="837" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C837" s="94"/>
+      <c r="C837" s="92"/>
     </row>
     <row r="838" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C838" s="94"/>
+      <c r="C838" s="92"/>
     </row>
     <row r="839" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C839" s="94"/>
+      <c r="C839" s="92"/>
     </row>
     <row r="840" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C840" s="94"/>
+      <c r="C840" s="92"/>
     </row>
     <row r="841" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C841" s="94"/>
+      <c r="C841" s="92"/>
     </row>
     <row r="842" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C842" s="94"/>
+      <c r="C842" s="92"/>
     </row>
     <row r="843" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C843" s="94"/>
+      <c r="C843" s="92"/>
     </row>
     <row r="844" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C844" s="94"/>
+      <c r="C844" s="92"/>
     </row>
     <row r="845" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C845" s="94"/>
+      <c r="C845" s="92"/>
     </row>
     <row r="846" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C846" s="94"/>
+      <c r="C846" s="92"/>
     </row>
     <row r="847" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C847" s="94"/>
+      <c r="C847" s="92"/>
     </row>
     <row r="848" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C848" s="94"/>
+      <c r="C848" s="92"/>
     </row>
     <row r="849" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C849" s="94"/>
+      <c r="C849" s="92"/>
     </row>
     <row r="850" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C850" s="94"/>
+      <c r="C850" s="92"/>
     </row>
     <row r="851" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C851" s="94"/>
+      <c r="C851" s="92"/>
     </row>
     <row r="852" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C852" s="94"/>
+      <c r="C852" s="92"/>
     </row>
     <row r="853" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C853" s="94"/>
+      <c r="C853" s="92"/>
     </row>
     <row r="854" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C854" s="94"/>
+      <c r="C854" s="92"/>
     </row>
     <row r="855" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C855" s="94"/>
+      <c r="C855" s="92"/>
     </row>
     <row r="856" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C856" s="94"/>
+      <c r="C856" s="92"/>
     </row>
     <row r="857" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C857" s="94"/>
+      <c r="C857" s="92"/>
     </row>
     <row r="858" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C858" s="94"/>
+      <c r="C858" s="92"/>
     </row>
     <row r="859" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C859" s="94"/>
+      <c r="C859" s="92"/>
     </row>
     <row r="860" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C860" s="94"/>
+      <c r="C860" s="92"/>
     </row>
     <row r="861" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C861" s="94"/>
+      <c r="C861" s="92"/>
     </row>
     <row r="862" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C862" s="94"/>
+      <c r="C862" s="92"/>
     </row>
     <row r="863" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C863" s="94"/>
+      <c r="C863" s="92"/>
     </row>
     <row r="864" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C864" s="94"/>
+      <c r="C864" s="92"/>
     </row>
     <row r="865" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C865" s="94"/>
+      <c r="C865" s="92"/>
     </row>
     <row r="866" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C866" s="94"/>
+      <c r="C866" s="92"/>
     </row>
     <row r="867" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C867" s="94"/>
+      <c r="C867" s="92"/>
     </row>
     <row r="868" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C868" s="94"/>
+      <c r="C868" s="92"/>
     </row>
     <row r="869" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C869" s="94"/>
+      <c r="C869" s="92"/>
     </row>
     <row r="870" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C870" s="94"/>
+      <c r="C870" s="92"/>
     </row>
     <row r="871" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C871" s="94"/>
+      <c r="C871" s="92"/>
     </row>
     <row r="872" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C872" s="94"/>
+      <c r="C872" s="92"/>
     </row>
     <row r="873" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C873" s="94"/>
+      <c r="C873" s="92"/>
     </row>
     <row r="874" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C874" s="94"/>
+      <c r="C874" s="92"/>
     </row>
     <row r="875" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C875" s="94"/>
+      <c r="C875" s="92"/>
     </row>
     <row r="876" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C876" s="94"/>
+      <c r="C876" s="92"/>
     </row>
     <row r="877" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C877" s="94"/>
+      <c r="C877" s="92"/>
     </row>
     <row r="878" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C878" s="94"/>
+      <c r="C878" s="92"/>
     </row>
     <row r="879" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C879" s="94"/>
+      <c r="C879" s="92"/>
     </row>
     <row r="880" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C880" s="94"/>
+      <c r="C880" s="92"/>
     </row>
     <row r="881" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C881" s="94"/>
+      <c r="C881" s="92"/>
     </row>
     <row r="882" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C882" s="94"/>
+      <c r="C882" s="92"/>
     </row>
     <row r="883" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C883" s="94"/>
+      <c r="C883" s="92"/>
     </row>
     <row r="884" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C884" s="94"/>
+      <c r="C884" s="92"/>
     </row>
     <row r="885" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C885" s="94"/>
+      <c r="C885" s="92"/>
     </row>
     <row r="886" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C886" s="94"/>
+      <c r="C886" s="92"/>
     </row>
     <row r="887" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C887" s="94"/>
+      <c r="C887" s="92"/>
     </row>
     <row r="888" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C888" s="94"/>
+      <c r="C888" s="92"/>
     </row>
     <row r="889" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C889" s="94"/>
+      <c r="C889" s="92"/>
     </row>
     <row r="890" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C890" s="94"/>
+      <c r="C890" s="92"/>
     </row>
     <row r="891" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C891" s="94"/>
+      <c r="C891" s="92"/>
     </row>
     <row r="892" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C892" s="94"/>
+      <c r="C892" s="92"/>
     </row>
     <row r="893" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C893" s="94"/>
+      <c r="C893" s="92"/>
     </row>
     <row r="894" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C894" s="94"/>
+      <c r="C894" s="92"/>
     </row>
     <row r="895" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C895" s="94"/>
+      <c r="C895" s="92"/>
     </row>
     <row r="896" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C896" s="94"/>
+      <c r="C896" s="92"/>
     </row>
     <row r="897" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C897" s="94"/>
+      <c r="C897" s="92"/>
     </row>
     <row r="898" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C898" s="94"/>
+      <c r="C898" s="92"/>
     </row>
     <row r="899" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C899" s="94"/>
+      <c r="C899" s="92"/>
     </row>
     <row r="900" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C900" s="94"/>
+      <c r="C900" s="92"/>
     </row>
     <row r="901" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C901" s="94"/>
+      <c r="C901" s="92"/>
     </row>
     <row r="902" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C902" s="94"/>
+      <c r="C902" s="92"/>
     </row>
     <row r="903" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C903" s="94"/>
+      <c r="C903" s="92"/>
     </row>
     <row r="904" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C904" s="94"/>
+      <c r="C904" s="92"/>
     </row>
     <row r="905" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C905" s="94"/>
+      <c r="C905" s="92"/>
     </row>
     <row r="906" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C906" s="94"/>
+      <c r="C906" s="92"/>
     </row>
     <row r="907" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C907" s="94"/>
+      <c r="C907" s="92"/>
     </row>
     <row r="908" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C908" s="94"/>
+      <c r="C908" s="92"/>
     </row>
     <row r="909" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C909" s="94"/>
+      <c r="C909" s="92"/>
     </row>
     <row r="910" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C910" s="94"/>
+      <c r="C910" s="92"/>
     </row>
     <row r="911" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C911" s="94"/>
+      <c r="C911" s="92"/>
     </row>
     <row r="912" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C912" s="94"/>
+      <c r="C912" s="92"/>
     </row>
     <row r="913" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C913" s="94"/>
+      <c r="C913" s="92"/>
     </row>
     <row r="914" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C914" s="94"/>
+      <c r="C914" s="92"/>
     </row>
     <row r="915" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C915" s="94"/>
+      <c r="C915" s="92"/>
     </row>
     <row r="916" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C916" s="94"/>
+      <c r="C916" s="92"/>
     </row>
     <row r="917" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C917" s="94"/>
+      <c r="C917" s="92"/>
     </row>
     <row r="918" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C918" s="94"/>
+      <c r="C918" s="92"/>
     </row>
     <row r="919" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C919" s="94"/>
+      <c r="C919" s="92"/>
     </row>
     <row r="920" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C920" s="94"/>
+      <c r="C920" s="92"/>
     </row>
     <row r="921" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C921" s="94"/>
+      <c r="C921" s="92"/>
     </row>
     <row r="922" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C922" s="94"/>
+      <c r="C922" s="92"/>
     </row>
     <row r="923" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C923" s="94"/>
+      <c r="C923" s="92"/>
     </row>
     <row r="924" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C924" s="94"/>
+      <c r="C924" s="92"/>
     </row>
     <row r="925" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C925" s="94"/>
+      <c r="C925" s="92"/>
     </row>
     <row r="926" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C926" s="94"/>
+      <c r="C926" s="92"/>
     </row>
     <row r="927" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C927" s="94"/>
+      <c r="C927" s="92"/>
     </row>
     <row r="928" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C928" s="94"/>
+      <c r="C928" s="92"/>
     </row>
     <row r="929" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C929" s="94"/>
+      <c r="C929" s="92"/>
     </row>
     <row r="930" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C930" s="94"/>
+      <c r="C930" s="92"/>
     </row>
     <row r="931" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C931" s="94"/>
+      <c r="C931" s="92"/>
     </row>
     <row r="932" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C932" s="94"/>
+      <c r="C932" s="92"/>
     </row>
     <row r="933" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C933" s="94"/>
+      <c r="C933" s="92"/>
     </row>
     <row r="934" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C934" s="94"/>
+      <c r="C934" s="92"/>
     </row>
     <row r="935" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C935" s="94"/>
+      <c r="C935" s="92"/>
     </row>
     <row r="936" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C936" s="94"/>
+      <c r="C936" s="92"/>
     </row>
     <row r="937" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C937" s="94"/>
+      <c r="C937" s="92"/>
     </row>
     <row r="938" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C938" s="94"/>
+      <c r="C938" s="92"/>
     </row>
     <row r="939" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C939" s="94"/>
+      <c r="C939" s="92"/>
     </row>
     <row r="940" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C940" s="94"/>
+      <c r="C940" s="92"/>
     </row>
     <row r="941" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C941" s="94"/>
+      <c r="C941" s="92"/>
     </row>
     <row r="942" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C942" s="94"/>
+      <c r="C942" s="92"/>
     </row>
     <row r="943" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C943" s="94"/>
+      <c r="C943" s="92"/>
     </row>
     <row r="944" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C944" s="94"/>
+      <c r="C944" s="92"/>
     </row>
     <row r="945" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C945" s="94"/>
+      <c r="C945" s="92"/>
     </row>
     <row r="946" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C946" s="94"/>
+      <c r="C946" s="92"/>
     </row>
     <row r="947" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C947" s="94"/>
+      <c r="C947" s="92"/>
     </row>
     <row r="948" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C948" s="94"/>
+      <c r="C948" s="92"/>
     </row>
     <row r="949" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C949" s="94"/>
+      <c r="C949" s="92"/>
     </row>
     <row r="950" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C950" s="94"/>
+      <c r="C950" s="92"/>
     </row>
     <row r="951" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C951" s="94"/>
+      <c r="C951" s="92"/>
     </row>
     <row r="952" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C952" s="94"/>
+      <c r="C952" s="92"/>
     </row>
     <row r="953" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C953" s="94"/>
+      <c r="C953" s="92"/>
     </row>
     <row r="954" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C954" s="94"/>
+      <c r="C954" s="92"/>
     </row>
     <row r="955" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C955" s="94"/>
+      <c r="C955" s="92"/>
     </row>
     <row r="956" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C956" s="94"/>
+      <c r="C956" s="92"/>
     </row>
     <row r="957" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C957" s="94"/>
+      <c r="C957" s="92"/>
     </row>
     <row r="958" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C958" s="94"/>
+      <c r="C958" s="92"/>
     </row>
     <row r="959" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C959" s="94"/>
+      <c r="C959" s="92"/>
     </row>
     <row r="960" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C960" s="94"/>
+      <c r="C960" s="92"/>
     </row>
     <row r="961" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C961" s="94"/>
+      <c r="C961" s="92"/>
     </row>
     <row r="962" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C962" s="94"/>
+      <c r="C962" s="92"/>
     </row>
     <row r="963" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C963" s="94"/>
+      <c r="C963" s="92"/>
     </row>
     <row r="964" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C964" s="94"/>
+      <c r="C964" s="92"/>
     </row>
     <row r="965" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C965" s="94"/>
+      <c r="C965" s="92"/>
     </row>
     <row r="966" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C966" s="94"/>
+      <c r="C966" s="92"/>
     </row>
     <row r="967" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C967" s="94"/>
+      <c r="C967" s="92"/>
     </row>
     <row r="968" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C968" s="94"/>
+      <c r="C968" s="92"/>
     </row>
     <row r="969" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C969" s="94"/>
+      <c r="C969" s="92"/>
     </row>
     <row r="970" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C970" s="94"/>
+      <c r="C970" s="92"/>
     </row>
     <row r="971" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C971" s="94"/>
+      <c r="C971" s="92"/>
     </row>
     <row r="972" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C972" s="94"/>
+      <c r="C972" s="92"/>
     </row>
     <row r="973" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C973" s="94"/>
+      <c r="C973" s="92"/>
     </row>
     <row r="974" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C974" s="94"/>
+      <c r="C974" s="92"/>
     </row>
     <row r="975" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C975" s="94"/>
+      <c r="C975" s="92"/>
     </row>
     <row r="976" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C976" s="94"/>
+      <c r="C976" s="92"/>
     </row>
     <row r="977" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C977" s="94"/>
+      <c r="C977" s="92"/>
     </row>
     <row r="978" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C978" s="94"/>
+      <c r="C978" s="92"/>
     </row>
     <row r="979" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C979" s="94"/>
+      <c r="C979" s="92"/>
     </row>
     <row r="980" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C980" s="94"/>
+      <c r="C980" s="92"/>
     </row>
     <row r="981" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C981" s="94"/>
+      <c r="C981" s="92"/>
     </row>
     <row r="982" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C982" s="94"/>
+      <c r="C982" s="92"/>
     </row>
     <row r="983" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C983" s="94"/>
+      <c r="C983" s="92"/>
     </row>
     <row r="984" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C984" s="94"/>
+      <c r="C984" s="92"/>
     </row>
     <row r="985" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C985" s="94"/>
+      <c r="C985" s="92"/>
     </row>
     <row r="986" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C986" s="94"/>
+      <c r="C986" s="92"/>
     </row>
     <row r="987" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C987" s="94"/>
+      <c r="C987" s="92"/>
     </row>
     <row r="988" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C988" s="94"/>
+      <c r="C988" s="92"/>
     </row>
     <row r="989" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C989" s="94"/>
+      <c r="C989" s="92"/>
     </row>
     <row r="990" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C990" s="94"/>
+      <c r="C990" s="92"/>
     </row>
     <row r="991" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C991" s="94"/>
+      <c r="C991" s="92"/>
     </row>
     <row r="992" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C992" s="94"/>
+      <c r="C992" s="92"/>
     </row>
     <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C993" s="94"/>
+      <c r="C993" s="92"/>
     </row>
     <row r="994" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C994" s="94"/>
+      <c r="C994" s="92"/>
     </row>
     <row r="995" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C995" s="94"/>
+      <c r="C995" s="92"/>
     </row>
     <row r="996" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C996" s="94"/>
+      <c r="C996" s="92"/>
     </row>
     <row r="997" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C997" s="94"/>
+      <c r="C997" s="92"/>
     </row>
     <row r="998" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C998" s="94"/>
+      <c r="C998" s="92"/>
     </row>
     <row r="999" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C999" s="94"/>
+      <c r="C999" s="92"/>
     </row>
     <row r="1000" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C1000" s="94"/>
+      <c r="C1000" s="92"/>
     </row>
     <row r="1001" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C1001" s="94"/>
+      <c r="C1001" s="92"/>
     </row>
     <row r="1002" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C1002" s="94"/>
+      <c r="C1002" s="92"/>
     </row>
     <row r="1003" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C1003" s="94"/>
+      <c r="C1003" s="92"/>
     </row>
     <row r="1004" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C1004" s="94"/>
+      <c r="C1004" s="92"/>
     </row>
     <row r="1005" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C1005" s="94"/>
+      <c r="C1005" s="92"/>
     </row>
     <row r="1006" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C1006" s="94"/>
+      <c r="C1006" s="92"/>
     </row>
     <row r="1007" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C1007" s="94"/>
+      <c r="C1007" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -9822,23 +9814,23 @@
       <c r="A2" s="31"/>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31"/>
       <c r="B3" s="31"/>
       <c r="C3" s="31"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="97"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="95"/>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="77"/>
-      <c r="B4" s="98" t="s">
+      <c r="A4" s="75"/>
+      <c r="B4" s="96" t="s">
         <v>150</v>
       </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="81" t="s">
+      <c r="C4" s="97"/>
+      <c r="D4" s="79" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="28" t="s">
@@ -9851,7 +9843,7 @@
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
-      <c r="D5" s="100" t="s">
+      <c r="D5" s="98" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="43" t="s">
@@ -9862,9 +9854,9 @@
       <c r="A6" s="45" t="s">
         <v>179</v>
       </c>
-      <c r="B6" s="85"/>
+      <c r="B6" s="83"/>
       <c r="C6" s="45"/>
-      <c r="D6" s="101" t="s">
+      <c r="D6" s="99" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="43" t="s">
@@ -9872,49 +9864,49 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="102" t="s">
+      <c r="A7" s="100" t="s">
         <v>180</v>
       </c>
-      <c r="B7" s="85"/>
-      <c r="C7" s="86"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="84"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="93"/>
     </row>
     <row r="8" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="45" t="s">
         <v>181</v>
       </c>
-      <c r="B8" s="85"/>
+      <c r="B8" s="83"/>
       <c r="C8" s="45"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
     </row>
     <row r="9" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="103" t="s">
+      <c r="A9" s="101" t="s">
         <v>173</v>
       </c>
-      <c r="B9" s="103"/>
-      <c r="C9" s="103"/>
-      <c r="D9" s="95"/>
-      <c r="E9" s="95"/>
+      <c r="B9" s="101"/>
+      <c r="C9" s="101"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
     </row>
     <row r="10" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="B10" s="87"/>
+      <c r="B10" s="85"/>
       <c r="C10" s="45"/>
-      <c r="D10" s="95"/>
-      <c r="E10" s="95"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
     </row>
     <row r="11" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="45" t="s">
         <v>183</v>
       </c>
-      <c r="B11" s="87"/>
+      <c r="B11" s="85"/>
       <c r="C11" s="45"/>
-      <c r="D11" s="95"/>
-      <c r="E11" s="95"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
     </row>
     <row r="12" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
@@ -9922,26 +9914,26 @@
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
     </row>
     <row r="13" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="45" t="s">
         <v>185</v>
       </c>
-      <c r="B13" s="87"/>
+      <c r="B13" s="85"/>
       <c r="C13" s="45"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="45" t="s">
         <v>186</v>
       </c>
-      <c r="B14" s="87"/>
+      <c r="B14" s="85"/>
       <c r="C14" s="45"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
+      <c r="D14" s="93"/>
+      <c r="E14" s="93"/>
     </row>
     <row r="15" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="54" t="s">
@@ -9949,161 +9941,161 @@
       </c>
       <c r="B15" s="54"/>
       <c r="C15" s="54"/>
-      <c r="D15" s="95"/>
-      <c r="E15" s="95"/>
+      <c r="D15" s="93"/>
+      <c r="E15" s="93"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="104" t="s">
+      <c r="A16" s="102" t="s">
         <v>188</v>
       </c>
-      <c r="B16" s="87"/>
+      <c r="B16" s="85"/>
       <c r="C16" s="45"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
     </row>
     <row r="17" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="B17" s="87"/>
+      <c r="B17" s="85"/>
       <c r="C17" s="45"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
     </row>
     <row r="18" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="45" t="s">
         <v>190</v>
       </c>
-      <c r="B18" s="87"/>
+      <c r="B18" s="85"/>
       <c r="C18" s="45"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="93"/>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="45" t="s">
         <v>191</v>
       </c>
-      <c r="B19" s="87"/>
+      <c r="B19" s="85"/>
       <c r="C19" s="45"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
     </row>
     <row r="20" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="45" t="s">
         <v>192</v>
       </c>
-      <c r="B20" s="87"/>
+      <c r="B20" s="85"/>
       <c r="C20" s="45"/>
     </row>
     <row r="21" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="71" t="s">
+      <c r="A21" s="70" t="s">
         <v>193</v>
       </c>
-      <c r="B21" s="71"/>
-      <c r="C21" s="71"/>
+      <c r="B21" s="70"/>
+      <c r="C21" s="70"/>
     </row>
     <row r="22" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="84" t="s">
+      <c r="A22" s="82" t="s">
         <v>194</v>
       </c>
-      <c r="B22" s="87"/>
+      <c r="B22" s="85"/>
       <c r="C22" s="45"/>
     </row>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="84" t="s">
+      <c r="A23" s="82" t="s">
         <v>195</v>
       </c>
-      <c r="B23" s="87"/>
-      <c r="C23" s="105"/>
+      <c r="B23" s="85"/>
+      <c r="C23" s="103"/>
     </row>
     <row r="24" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="106" t="s">
+      <c r="A24" s="104" t="s">
         <v>196</v>
       </c>
-      <c r="B24" s="106"/>
-      <c r="C24" s="106"/>
+      <c r="B24" s="104"/>
+      <c r="C24" s="104"/>
     </row>
     <row r="25" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="45" t="s">
         <v>197</v>
       </c>
-      <c r="B25" s="87"/>
+      <c r="B25" s="85"/>
       <c r="C25" s="45"/>
     </row>
     <row r="26" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="45" t="s">
         <v>198</v>
       </c>
-      <c r="B26" s="87"/>
+      <c r="B26" s="85"/>
       <c r="C26" s="45"/>
     </row>
     <row r="27" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="B27" s="87"/>
+      <c r="B27" s="85"/>
       <c r="C27" s="45"/>
     </row>
     <row r="28" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="45" t="s">
         <v>200</v>
       </c>
-      <c r="B28" s="87"/>
+      <c r="B28" s="85"/>
       <c r="C28" s="45"/>
     </row>
     <row r="29" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="B29" s="87"/>
+      <c r="B29" s="85"/>
       <c r="C29" s="45"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="94"/>
+      <c r="B30" s="92"/>
     </row>
     <row r="31" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="93"/>
+      <c r="B31" s="91"/>
       <c r="C31" s="43"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="92"/>
-      <c r="B32" s="93"/>
+      <c r="A32" s="90"/>
+      <c r="B32" s="91"/>
       <c r="C32" s="43"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="92"/>
-      <c r="B33" s="93"/>
+      <c r="A33" s="90"/>
+      <c r="B33" s="91"/>
       <c r="C33" s="43"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="92"/>
-      <c r="B34" s="93"/>
+      <c r="A34" s="90"/>
+      <c r="B34" s="91"/>
       <c r="C34" s="43"/>
-      <c r="D34" s="95"/>
-      <c r="E34" s="95"/>
+      <c r="D34" s="93"/>
+      <c r="E34" s="93"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="92"/>
-      <c r="B35" s="93"/>
+      <c r="A35" s="90"/>
+      <c r="B35" s="91"/>
       <c r="C35" s="43"/>
-      <c r="D35" s="95"/>
-      <c r="E35" s="95"/>
+      <c r="D35" s="93"/>
+      <c r="E35" s="93"/>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="92"/>
-      <c r="B36" s="93"/>
+      <c r="A36" s="90"/>
+      <c r="B36" s="91"/>
       <c r="C36" s="43"/>
-      <c r="D36" s="95"/>
-      <c r="E36" s="95"/>
+      <c r="D36" s="93"/>
+      <c r="E36" s="93"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="95"/>
-      <c r="C37" s="95"/>
-      <c r="D37" s="95"/>
-      <c r="E37" s="95"/>
+      <c r="B37" s="93"/>
+      <c r="C37" s="93"/>
+      <c r="D37" s="93"/>
+      <c r="E37" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="9">
